--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45727</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>44867</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45203</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>44564</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45665</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45460</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45902</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45378</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44673</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44473</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44787</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44505</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45432</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45763</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45534</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45162</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44943</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45841</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45203</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44589</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45384</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45012</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45988</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45832</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44936</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45106</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46280</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45397</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45644</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45646</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45728</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44512</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44735</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44475</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44488</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44719</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44552</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44580</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44886</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44750</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44552</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44776</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44581</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44824</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44735</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44466</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44745</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44494</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44624</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44468</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44543</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44505</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44676</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44780</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44780</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44511</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44846</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44840</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44557</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44780</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44607</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44602</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44868</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44649</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44550</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44538</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44819</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44806</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44616</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44719</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44644</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44826</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44683</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44679</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44686</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44518</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44698</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44829</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45425</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44825</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44546</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45278</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>45306</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>45050</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>45050</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>45621</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45425</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45720</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45253</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>45747</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45266</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45279</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44745</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45171</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45740</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45740</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>44606</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>44512</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45278</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45278</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44709</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45173</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45631</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44627</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45238</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45005</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45747</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45231</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44823</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45372</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45736</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44830</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45107</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>45558</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44852</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45454</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>44487</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>45226</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45331</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>45699</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44720</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44763</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45729</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45398</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45374</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45374</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44538</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45676</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45460</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45222</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45506</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45264</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45189</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>44881</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45699</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45728</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45113</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45516</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45589</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>44823</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44945</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44819</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>44993</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45711</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44924</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>44490</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45740</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44635</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44853</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45659</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45082</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45251</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>44900</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45471</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45471</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45147</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>45411</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45253</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>45146</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>45716</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>45403</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44608</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44609</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44896</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44976</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45667</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45667</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45667</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44587</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44564</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44629</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44734</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44993</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45212</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45608</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45055</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44509</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45099</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45107</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45012</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45156</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44550</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45609</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>45582</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>45735</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>45728</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>44910</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45740</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45932</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45729</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>46139</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45905</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>45148</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44762</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>45113</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45888</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45888</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>44985</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>45453</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>45208</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45888</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
         <v>44994</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45771</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45880</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>45834</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44606</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>45890</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>44880</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45278</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45356</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>45343</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45895</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45895</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45189</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45893</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>45893</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45893</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45893</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45334</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45245</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45895</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45711</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45714</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>45168</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45239</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45481</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>45898</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45901</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45922</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45888</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44936</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>45418</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45089</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45391</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         <v>45896</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45874</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45902</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>46139</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45704</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45820</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45831</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45904</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45904</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45908</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45901</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>45723</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45621</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45894</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45301</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45576</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45735</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45910</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45910</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45204</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45595</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45910</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45912</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45915</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44659</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45012</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45278</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44916</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>44943</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45912</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>44671</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44607</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45358</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45282</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45191</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45719</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45278</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45924</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45924</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45855</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45925</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45387</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45342</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>44580</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46142</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45931</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>44564</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45237</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>45677</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45555</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>46146</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45249</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45523</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45280</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44663</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45471</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>45324</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45938</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45937</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45005</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>45943</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>46149</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>45944</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44550</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45945</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>46148</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45527</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45946</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>45572</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>45949</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45950</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>45295</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45330</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45176</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45880</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45367</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>44988</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45603</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45133</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45961</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>45733</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45439</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>46155</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45719</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29005,7 +29005,7 @@
         <v>45261</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         <v>44777</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45428</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45837</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45356</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45394</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>45146</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>44678</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45603</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45975</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45379</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45419</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>45975</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>45977</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>44881</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45337</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>46154</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>45258</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45980</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45982</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44468</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45611</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>44509</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45983</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45982</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>46198</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45525</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45542</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45988</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45988</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45719</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45989</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45989</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45988</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>45988</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>45989</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45989</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>45988</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45890</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45992</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45425</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45993</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>45603</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>46059</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45825</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45931</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45805</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45006</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45477</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45993</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45639</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45639</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45450</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45995</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44813</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45728</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45107</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>45995</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>44960</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>46164</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45457</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>45988</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45988</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>45988</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45988</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45775</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45522</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>46164</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45356</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45352</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>46167</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>46006</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45433</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45044</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>46010</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45222</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45428</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45548</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45439</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>45313</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>46170</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45021</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>45271</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>46170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>44509</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46170</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46170</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>46030</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35454,7 +35454,7 @@
         <v>46030</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>46030</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35600,7 +35600,7 @@
         <v>46170</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>46170</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>45266</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>46034</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45534</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>46037</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>46174</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>45156</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>46041</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>46041</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>46041</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>44868</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45147</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45191</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>44552</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>46043</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45062</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>44463</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>46170</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>46045</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>46045</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>46045</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45237</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45348</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>46046</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>46176</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>46046</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>44909</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>46175</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>45771</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>45564</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>46055</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45609</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>45078</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>46055</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>44824</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45559</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>46177</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>44603</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>44501</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>46058</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45012</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45127</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>46059</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45720</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45583</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45355</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46065</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>46182</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45171</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46072</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46073</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45721</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45631</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45586</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46078</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45068</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>45534</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>46079</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>46079</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>46079</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>45070</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44938</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>46050</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>46083</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>44745</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46083</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46083</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>46083</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>46083</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>46083</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>46086</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45368</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45454</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46090</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>46087</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>46090</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>45098</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45524</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>45597</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45597</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>46087</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>46087</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>46062</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44861</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>46090</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>45989</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>44763</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45278</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>46092</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>46093</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45495</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>46094</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>46093</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>45575</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45211</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45211</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>44487</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         <v>45516</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>45516</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>45237</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>46101</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>46101</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>46104</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>46191</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45223</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>46106</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44509</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>46105</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45392</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>46108</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>46111</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>46111</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45712</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45089</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>44876</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>46119</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>46119</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>45457</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>46120</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>45341</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>46122</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45547</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45707</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>46183</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45156</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46203</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>44880</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>45635</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45253</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>45233</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>44881</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45349,7 +45349,7 @@
         <v>44886</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45180</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>46134</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>45474</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45569</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45387</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45779</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>44523</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>44980</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46006,7 +46006,7 @@
         <v>45706</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45685</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46152,7 +46152,7 @@
         <v>45727</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46225,7 +46225,7 @@
         <v>45874</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>46139</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46371,7 +46371,7 @@
         <v>44879</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46444,7 +46444,7 @@
         <v>44952</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46517,7 +46517,7 @@
         <v>45832</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46590,7 +46590,7 @@
         <v>45807</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>45807</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46736,7 +46736,7 @@
         <v>44572</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45912</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>44812</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>45874</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45932</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45095</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>44488</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45267</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>46206</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>45397</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>44758</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45558</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>45704</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45607</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>46251</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45740</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>46251</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>45625</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>46251</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>46251</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45573</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44581</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>46105</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>44938</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45567</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>46209</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45107</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>46209</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45527</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>44523</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>46209</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>46209</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>46209</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49160,7 +49160,7 @@
         <v>46209</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         <v>44994</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>46255</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45685</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45728</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45106</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>46253</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45700</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>44929</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45426</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>46255</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45229</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45191</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45191</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>44959</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45237</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>44921</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45720</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45692</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45692</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>44679</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50703,7 +50703,7 @@
         <v>45063</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45420</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50849,7 +50849,7 @@
         <v>44973</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45517</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>45681</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45385</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45491</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45441</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>45075</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>46258</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>44671</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51506,7 +51506,7 @@
         <v>45063</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45707</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51652,7 +51652,7 @@
         <v>45040</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45365</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51798,7 +51798,7 @@
         <v>45281</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45098</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>45098</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45386</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>46262</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>44509</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>44998</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>44574</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45361</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>45314</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52533,7 +52533,7 @@
         <v>45057</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>44868</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45769</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45149</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>46266</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>45273</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>46266</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>46266</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53122,7 +53122,7 @@
         <v>45677</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>45040</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53268,7 +53268,7 @@
         <v>45393</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53341,7 +53341,7 @@
         <v>44623</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53414,7 +53414,7 @@
         <v>45194</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53487,7 +53487,7 @@
         <v>45672</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53560,7 +53560,7 @@
         <v>44489</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>46269</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>46269</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53779,7 +53779,7 @@
         <v>45380</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         <v>45783</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53925,7 +53925,7 @@
         <v>45369</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53998,7 +53998,7 @@
         <v>45427</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54071,7 +54071,7 @@
         <v>46273</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>46273</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54217,7 +54217,7 @@
         <v>45555</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>45784</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>46232</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54436,7 +54436,7 @@
         <v>46232</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>46232</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54582,7 +54582,7 @@
         <v>46279</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45681</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54728,7 +54728,7 @@
         <v>45646</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>45736</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>46233</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>46237</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>46237</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>46237</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>45720</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>46279</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>44881</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55390,7 +55390,7 @@
         <v>46237</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>46237</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>46279</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55609,7 +55609,7 @@
         <v>46281</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45791</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55760,7 +55760,7 @@
         <v>45790</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>46281</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45790</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45791</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45791</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45790</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>46113</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45790</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45790</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>45790</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56520,7 +56520,7 @@
         <v>46283</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>45239</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45796</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45707</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         <v>46283</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56890,7 +56890,7 @@
         <v>45323</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56963,7 +56963,7 @@
         <v>45638</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>46283</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57114,7 +57114,7 @@
         <v>45799</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57187,7 +57187,7 @@
         <v>45800</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57260,7 +57260,7 @@
         <v>45807</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57333,7 +57333,7 @@
         <v>45615</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57406,7 +57406,7 @@
         <v>45811</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57479,7 +57479,7 @@
         <v>45520</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>45811</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57625,7 +57625,7 @@
         <v>45582</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45811</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57776,7 +57776,7 @@
         <v>45503</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57849,7 +57849,7 @@
         <v>45358</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57922,7 +57922,7 @@
         <v>45630</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57995,7 +57995,7 @@
         <v>44872</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58068,7 +58068,7 @@
         <v>45771</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>45607</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58214,7 +58214,7 @@
         <v>45813</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58287,7 +58287,7 @@
         <v>45575</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45419</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58433,7 +58433,7 @@
         <v>45623</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45763</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58579,7 +58579,7 @@
         <v>45646</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58652,7 +58652,7 @@
         <v>45761</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58725,7 +58725,7 @@
         <v>45646</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58798,7 +58798,7 @@
         <v>45817</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58871,7 +58871,7 @@
         <v>45818</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58944,7 +58944,7 @@
         <v>45757</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59017,7 +59017,7 @@
         <v>45825</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59090,7 +59090,7 @@
         <v>45831</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45831</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59236,7 +59236,7 @@
         <v>45831</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59309,7 +59309,7 @@
         <v>45832</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59382,7 +59382,7 @@
         <v>45835</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45841</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45842</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45842</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45358</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>45832</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45808</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>45847</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45847</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>45847</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60117,7 +60117,7 @@
         <v>45847</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>45847</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>45871</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60336,7 +60336,7 @@
         <v>45874</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         <v>45874</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60482,7 +60482,7 @@
         <v>45310</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60555,7 +60555,7 @@
         <v>45746</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60628,7 +60628,7 @@
         <v>45537</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60701,7 +60701,7 @@
         <v>45497</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60774,7 +60774,7 @@
         <v>45769</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60847,7 +60847,7 @@
         <v>45817</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60920,7 +60920,7 @@
         <v>45877</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -60993,7 +60993,7 @@
         <v>45883</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61071,7 +61071,7 @@
         <v>44579</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>44540</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61227,7 +61227,7 @@
         <v>44911</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61305,7 +61305,7 @@
         <v>44911</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>44540</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>44911</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61539,7 +61539,7 @@
         <v>44540</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>45351</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61695,7 +61695,7 @@
         <v>44911</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61773,7 +61773,7 @@
         <v>45299</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61846,7 +61846,7 @@
         <v>44579</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>44540</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>45351</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62080,7 +62080,7 @@
         <v>44540</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>44579</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>44540</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62314,7 +62314,7 @@
         <v>44501</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62387,7 +62387,7 @@
         <v>45779</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62460,7 +62460,7 @@
         <v>46035</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>46177</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62616,7 +62616,7 @@
         <v>46203</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44867</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>45727</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44564</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45203</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45237</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45303</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45902</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45665</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45378</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45460</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44473</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44787</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44505</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45323</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45397</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44943</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45832</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45432</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>45646</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45841</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45763</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45203</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45162</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46280</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44936</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45012</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45384</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45644</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45534</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44735</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44830</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44629</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44629</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44475</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44488</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44719</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44580</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44552</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44886</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44750</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44552</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44776</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44581</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44824</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44735</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44466</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44745</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44494</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44624</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44468</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44543</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44505</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44676</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44780</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44780</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44511</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44846</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44840</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44557</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44780</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44607</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44602</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44868</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44649</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44550</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44538</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44819</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44806</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44616</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44719</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44644</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44826</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44683</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44679</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44686</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44518</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44698</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>44820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44829</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45712</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45208</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45367</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45385</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45392</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45428</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45471</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45261</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45558</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45386</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44868</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45454</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45237</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44550</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45457</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44825</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44861</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45453</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45278</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45573</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45107</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45439</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>45707</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>45796</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45306</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45454</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45323</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>46030</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>44881</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45342</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45638</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>46030</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>46034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45877</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45817</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45888</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44509</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45589</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45888</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44512</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45834</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45888</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45516</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45253</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45890</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45420</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45428</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45893</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45893</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45729</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45893</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45893</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44564</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44993</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>45631</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>46041</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45050</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>46041</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45418</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45524</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>46043</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45148</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45113</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45113</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46046</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>46045</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>46046</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45075</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45902</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44876</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45888</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45901</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45194</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45534</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45904</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45491</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45547</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45901</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45799</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45800</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46055</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46055</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45910</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45910</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45912</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45912</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>46058</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45343</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44627</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45575</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45617</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>46059</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>46065</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44580</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45740</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>44720</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45231</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45233</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45924</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45098</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45012</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45924</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45925</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45569</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46072</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46073</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>46079</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>46079</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>46078</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>46079</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46083</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>46083</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44574</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45931</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>46083</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>46083</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>46083</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44943</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45564</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>46050</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45520</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45222</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45358</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44985</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>46087</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>46087</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>44659</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>46087</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45582</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44872</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>46086</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45989</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>44678</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>46090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45503</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45615</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46090</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>46090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45938</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46093</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45937</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>46092</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46093</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45707</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44980</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45943</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45630</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45807</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44745</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45238</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45944</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45426</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>46101</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45945</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46101</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45946</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45559</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44679</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>46105</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45949</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45950</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45156</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45397</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46104</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45168</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45095</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44994</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45603</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45607</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45068</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45811</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44489</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>46111</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45880</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>46111</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45266</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46108</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45811</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45716</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45237</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>46119</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>46119</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45575</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45006</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45961</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>46122</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45567</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45771</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45811</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45419</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45471</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45813</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45757</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45818</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45189</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45977</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44509</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44993</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44973</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45975</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45975</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45980</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>46134</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45982</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46134</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45982</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45267</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45623</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45983</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45988</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45672</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45931</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45988</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45988</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>44762</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45988</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45988</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45831</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45992</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45989</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45874</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45989</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45763</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45771</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45699</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45989</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45481</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45894</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45993</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44572</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45993</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44879</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>44523</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45728</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45995</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45704</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45995</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45189</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45005</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45807</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45807</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45113</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45387</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45932</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45761</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>44910</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45820</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45706</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>45692</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45692</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45646</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45905</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45779</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44564</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45988</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>45988</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45966</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>46006</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45988</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45988</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45012</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45021</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45922</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45880</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45685</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45677</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45735</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45874</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45912</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46139</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45775</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46010</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44830</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45171</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44880</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>45855</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44490</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45711</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>46139</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45676</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45874</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45932</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45832</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45896</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44538</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45740</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45586</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45253</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45525</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45727</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>46139</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45847</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45609</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45714</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45825</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45720</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44629</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45191</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45082</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45611</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45249</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45735</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>45721</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44812</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45595</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>46142</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>45831</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45280</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45226</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45831</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45831</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46146</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>46148</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>44813</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>44936</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46149</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45229</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45832</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>44881</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45771</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>44880</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45609</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45078</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45379</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45747</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45089</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>46154</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>46155</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44487</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45837</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>46198</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45740</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45835</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>46059</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45278</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45890</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45542</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45825</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45548</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45356</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45099</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>44758</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45368</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>45063</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45841</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>44509</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45842</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45931</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45356</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46164</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45805</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45832</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45331</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>45273</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45358</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>46164</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45398</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45847</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45847</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45847</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45847</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>45847</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45191</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45808</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44976</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45374</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45374</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>46167</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>46170</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>46170</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45425</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>46170</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>46170</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>46170</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>46170</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>46170</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>46175</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>45266</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44994</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45603</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>46174</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45204</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45558</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>46176</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>46177</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>45348</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45355</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45607</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45314</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>44509</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45527</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>46182</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45582</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45874</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45044</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45723</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>45874</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45393</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45719</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>45191</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>45460</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41634,7 +41634,7 @@
         <v>45871</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>46062</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45146</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>45534</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45334</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45667</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45089</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45537</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>45746</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>44509</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45310</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>45769</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>44603</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>44550</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45439</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45497</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>46191</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45625</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>45506</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44581</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>46203</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>44607</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>46183</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45146</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45711</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>44606</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44587</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44606</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45883</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>46251</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>46251</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>46209</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>46209</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>46209</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>46105</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>46209</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45621</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>46251</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>46251</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45313</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>45107</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>46209</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>46209</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>44635</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45098</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>45057</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>46253</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>44663</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>46255</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>45704</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>46255</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45147</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45583</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45222</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>44763</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45237</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45769</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45171</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45976,7 +45976,7 @@
         <v>46258</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>45211</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46122,7 +46122,7 @@
         <v>45659</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45212</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>44823</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>45681</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>45191</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>45699</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45729</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45223</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45517</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>45278</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45278</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>45295</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47018,7 +47018,7 @@
         <v>45278</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45180</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>46266</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>46266</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45733</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>45728</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>46266</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>46262</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>45278</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>44853</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47753,7 +47753,7 @@
         <v>45352</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45330</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>44988</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45258</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>46269</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>46269</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>46273</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>44938</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45264</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44852</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45098</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>46273</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>45239</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>44868</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45281</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>46233</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>46232</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>45736</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45728</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>44623</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>46232</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>46232</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>46279</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49432,7 +49432,7 @@
         <v>45700</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45527</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>46279</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>46237</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>46237</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>46237</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>45301</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>46279</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>44924</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45728</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>46237</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>46237</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45211</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>46113</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>46281</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45740</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45740</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45621</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>46281</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>45597</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>44900</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>46283</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>44960</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>45608</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45391</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>46283</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51345,7 +51345,7 @@
         <v>46283</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45450</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45040</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>46287</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>46287</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>44824</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51798,7 +51798,7 @@
         <v>45572</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45910</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>45895</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>44745</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45271</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>46288</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>45989</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>44763</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45419</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44552</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>44819</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45063</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45341</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45387</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45403</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>44671</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45251</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>44501</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>44909</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>44671</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45516</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45516</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>44777</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45425</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45012</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>46289</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         <v>44488</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>45597</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44468</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>45425</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45572</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>44608</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54149,7 +54149,7 @@
         <v>45040</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>44952</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>45237</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45555</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45631</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>45106</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45433</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45471</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54733,7 +54733,7 @@
         <v>45372</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>45245</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45394</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45253</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45156</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45107</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>44998</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>44823</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45457</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>44929</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45523</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>45358</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45062</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>44523</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45522</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45495</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45149</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>44487</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45127</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56130,7 +56130,7 @@
         <v>45667</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>44916</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45266</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>44546</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>45147</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56500,7 +56500,7 @@
         <v>44609</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45411</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45365</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45324</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56792,7 +56792,7 @@
         <v>45055</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45356</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56943,7 +56943,7 @@
         <v>45719</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57016,7 +57016,7 @@
         <v>44709</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45005</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>45279</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>44896</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45474</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>44921</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>45361</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45477</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>44959</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>44945</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45156</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45635</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57897,7 +57897,7 @@
         <v>45133</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45278</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58043,7 +58043,7 @@
         <v>45176</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>44881</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>44886</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>45173</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45677</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45337</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>45107</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58554,7 +58554,7 @@
         <v>45667</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45712</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>44734</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>45747</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58851,7 +58851,7 @@
         <v>45441</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>45707</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45603</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59070,7 +59070,7 @@
         <v>45685</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>45576</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>45639</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>45639</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>45380</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45646</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45784</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>45369</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45783</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59727,7 +59727,7 @@
         <v>45736</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59800,7 +59800,7 @@
         <v>45681</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>45427</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59946,7 +59946,7 @@
         <v>45555</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>45790</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60097,7 +60097,7 @@
         <v>45790</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>45790</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60248,7 +60248,7 @@
         <v>45720</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60326,7 +60326,7 @@
         <v>44881</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>45790</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>45790</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60555,7 +60555,7 @@
         <v>45790</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45791</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>45791</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>45791</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>44579</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>44579</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>44579</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>44540</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>44911</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>44911</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>44540</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>44911</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61486,7 +61486,7 @@
         <v>44540</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>45351</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61642,7 +61642,7 @@
         <v>44911</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>45299</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>44540</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45351</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61949,7 +61949,7 @@
         <v>44540</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62027,7 +62027,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62105,7 +62105,7 @@
         <v>44501</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62178,7 +62178,7 @@
         <v>45779</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62251,7 +62251,7 @@
         <v>46035</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62329,7 +62329,7 @@
         <v>46177</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>46203</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44867</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>45727</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44564</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45203</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45237</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45303</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45902</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45665</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45378</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45460</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44473</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44787</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44505</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45323</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45397</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44943</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45832</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45432</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>45646</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45841</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45763</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>45203</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45162</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>46280</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44936</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45012</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45384</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45644</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45534</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44735</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44830</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44629</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44629</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44475</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44488</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44719</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44580</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44552</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44886</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44750</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44552</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44776</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44581</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44824</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44735</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44466</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44745</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44494</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44624</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44491</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44468</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44543</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44505</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44676</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44629</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44719</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44780</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44780</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44511</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44846</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44840</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44840</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44557</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44861</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44780</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44607</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44607</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44602</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44868</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44649</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44550</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44538</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44819</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44806</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44526</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44616</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44719</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44644</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44826</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44683</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44679</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44686</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44518</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44698</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>44820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44829</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45712</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45208</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45367</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>45720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45385</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45392</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45428</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45471</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45261</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45558</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45386</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44868</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45454</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45070</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45237</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44550</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45457</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44825</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44861</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45453</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45278</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45573</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45107</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44938</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45439</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>45707</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>45796</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45306</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45454</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45323</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>46030</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>44881</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45342</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45638</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>46030</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>46030</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>46034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45877</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45817</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45888</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44509</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45589</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45888</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>44512</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45834</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45888</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45516</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45253</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45890</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45420</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45428</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45893</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45893</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45729</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45893</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45893</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44564</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>44993</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>45631</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>46041</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45050</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45050</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>46041</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45418</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45524</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>46043</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45148</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45113</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45113</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46046</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>46045</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>46046</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>45075</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45902</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44876</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45888</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>46045</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45901</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45194</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>45534</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45904</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45491</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45547</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45901</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45799</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45800</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46055</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46055</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45910</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45910</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45912</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45912</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>46058</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45343</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44627</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45575</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45617</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>46059</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>46065</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44580</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45740</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>44720</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45231</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45233</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45924</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45098</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45012</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45924</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45925</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45569</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46072</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46073</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>46079</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>46079</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>46078</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>46079</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46083</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>46083</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44574</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45931</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>46083</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>46083</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>46083</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44943</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45564</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>46050</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45520</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45222</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45358</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44985</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>46087</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>46087</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>44659</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>46087</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45582</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44872</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>46086</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45989</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>44678</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>46090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45503</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45615</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46090</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>46090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45938</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46093</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45937</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>46092</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46093</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45707</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44980</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45943</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45630</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45807</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44745</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45238</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45944</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45426</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>46101</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45945</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46101</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45946</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45559</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44679</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>46105</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45949</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45950</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45156</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45397</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46104</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45168</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45095</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44994</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45603</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45607</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45068</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45811</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44489</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>46111</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45880</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>46111</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45266</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46108</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45811</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45716</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45237</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>46119</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>46119</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45575</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45006</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>45961</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>46122</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>45567</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45771</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>45811</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45419</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45471</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45813</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>45757</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45818</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45189</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45977</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>44509</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>44993</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>44973</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45975</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45975</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45980</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>46134</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45982</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46134</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45982</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45267</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45623</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45983</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45988</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45672</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45931</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45988</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45988</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>44762</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45988</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45988</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45831</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45646</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45992</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45989</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45874</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45989</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45763</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45771</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45699</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45989</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45481</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45894</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45993</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44572</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45993</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44879</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>44523</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45728</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45995</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45704</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45995</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45189</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45005</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45807</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45807</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45113</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45113</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45387</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45932</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45761</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>44910</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45820</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45706</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>45692</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45692</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45646</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45905</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45779</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44564</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45988</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>45988</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45966</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>46006</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45988</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45988</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45012</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45021</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45922</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45880</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45685</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45677</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45735</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45874</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45912</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46139</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45775</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46010</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44830</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45171</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44880</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>45855</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44490</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45711</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>46139</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45676</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45874</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45932</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>45832</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45896</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44538</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>45740</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45586</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45253</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45525</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45727</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>46139</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45847</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45609</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45714</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45825</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>45720</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44629</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45191</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>45082</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45611</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45249</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45735</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>45721</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44812</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45595</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>46142</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>45831</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45280</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45226</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45831</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45831</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46146</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>46148</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>44813</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>44936</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>46149</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45229</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45832</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>44881</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45771</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>44880</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45609</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45078</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45379</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45747</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45089</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>46154</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>46155</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>44487</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45837</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>46198</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45740</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45835</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36557,7 +36557,7 @@
         <v>46059</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45278</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45890</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45542</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45825</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45548</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>45356</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45099</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>44758</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37224,7 +37224,7 @@
         <v>45368</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37297,7 +37297,7 @@
         <v>45063</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45841</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>44509</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45842</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45931</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45356</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46164</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45805</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45832</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45331</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>45273</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45358</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>46164</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>45398</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>45847</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45847</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45847</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45847</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>45847</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45191</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45808</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>44976</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45374</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45374</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>46167</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>46170</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>46170</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45425</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>46170</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>46170</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>46170</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>46170</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>46170</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>46175</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>45266</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>44994</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45603</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>46174</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45204</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45558</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>46176</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>46177</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>45348</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45355</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45607</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>45314</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>44509</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45527</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>46182</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45582</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45874</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45044</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45723</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>45874</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>45393</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45719</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>45191</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>45460</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41634,7 +41634,7 @@
         <v>45871</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41707,7 +41707,7 @@
         <v>46062</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41780,7 +41780,7 @@
         <v>45146</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>45534</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45334</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45667</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45089</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45537</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>45746</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>44509</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45310</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>45769</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>44603</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>44550</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45439</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42734,7 +42734,7 @@
         <v>45497</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>46191</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45625</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42953,7 +42953,7 @@
         <v>45506</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44581</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>46203</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>44607</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>46183</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>45146</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43396,7 +43396,7 @@
         <v>45711</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>44606</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43542,7 +43542,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44587</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44606</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43761,7 +43761,7 @@
         <v>45883</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43839,7 +43839,7 @@
         <v>46251</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>46251</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>46209</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>46209</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>46209</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>46105</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>46209</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45621</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>46251</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>46251</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45313</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>45107</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>46209</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>46209</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>44635</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45098</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>45057</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>46253</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>44663</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>46255</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>45704</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>46255</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45147</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>45583</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45601,7 +45601,7 @@
         <v>45222</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>44763</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45237</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45825,7 +45825,7 @@
         <v>45769</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45171</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45976,7 +45976,7 @@
         <v>46258</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>45211</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46122,7 +46122,7 @@
         <v>45659</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45212</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>44823</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>45681</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46414,7 +46414,7 @@
         <v>45191</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>45699</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45729</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45223</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45517</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>45278</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45278</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>45295</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47018,7 +47018,7 @@
         <v>45278</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45180</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>46266</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>46266</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45733</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>45728</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>46266</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>46262</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>45278</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>44853</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47753,7 +47753,7 @@
         <v>45352</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45330</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>44988</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45258</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>46269</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>46269</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>46273</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>44938</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48337,7 +48337,7 @@
         <v>45264</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44852</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45098</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>46273</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>45239</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>44868</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45281</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>46233</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>46232</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>45736</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45728</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>44623</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>46232</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>46232</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>46279</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49432,7 +49432,7 @@
         <v>45700</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45527</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>46279</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>46237</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>46237</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>46237</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>45301</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49943,7 +49943,7 @@
         <v>46279</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>44924</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45728</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>46237</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>46237</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45211</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>46113</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>46281</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45740</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45740</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45621</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>46281</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>45597</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>44900</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>46283</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>44960</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>45608</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45391</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>46283</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51345,7 +51345,7 @@
         <v>46283</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45450</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45040</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>46287</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>46287</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>44824</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51798,7 +51798,7 @@
         <v>45572</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45910</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>45895</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>44745</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45271</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>46288</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>45989</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>44763</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45419</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>44552</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>44819</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45063</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45341</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45387</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45403</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>44671</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45251</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>44501</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>44909</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>44671</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45516</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>45516</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>44777</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45425</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>45012</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>46289</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         <v>44488</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>45597</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44468</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>45425</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45572</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>44608</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54149,7 +54149,7 @@
         <v>45040</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54222,7 +54222,7 @@
         <v>44952</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54295,7 +54295,7 @@
         <v>45237</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
         <v>45555</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45631</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>45106</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45433</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45471</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54733,7 +54733,7 @@
         <v>45372</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>45245</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45394</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45253</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45156</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45107</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>44998</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>44823</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45457</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>44929</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45523</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>45358</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45062</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>44523</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45522</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45495</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45149</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>44487</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45127</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56130,7 +56130,7 @@
         <v>45667</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>44916</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45266</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>44546</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>45147</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56500,7 +56500,7 @@
         <v>44609</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45411</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45365</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45324</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56792,7 +56792,7 @@
         <v>45055</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45356</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56943,7 +56943,7 @@
         <v>45719</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57016,7 +57016,7 @@
         <v>44709</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45005</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>45279</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>44896</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45474</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>44921</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>45361</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45477</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>44959</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>44945</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45156</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57824,7 +57824,7 @@
         <v>45635</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57897,7 +57897,7 @@
         <v>45133</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57970,7 +57970,7 @@
         <v>45278</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58043,7 +58043,7 @@
         <v>45176</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>44881</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>44886</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>45173</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58335,7 +58335,7 @@
         <v>45677</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45337</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>45107</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58554,7 +58554,7 @@
         <v>45667</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>45712</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58700,7 +58700,7 @@
         <v>44734</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>45747</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58851,7 +58851,7 @@
         <v>45441</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58924,7 +58924,7 @@
         <v>45707</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45603</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59070,7 +59070,7 @@
         <v>45685</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>45576</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>45639</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>45639</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>45380</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45646</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>45784</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>45369</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45783</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59727,7 +59727,7 @@
         <v>45736</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59800,7 +59800,7 @@
         <v>45681</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>45427</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59946,7 +59946,7 @@
         <v>45555</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60019,7 +60019,7 @@
         <v>45790</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60097,7 +60097,7 @@
         <v>45790</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>45790</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60248,7 +60248,7 @@
         <v>45720</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60326,7 +60326,7 @@
         <v>44881</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>45790</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>45790</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60555,7 +60555,7 @@
         <v>45790</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45791</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>45791</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>45791</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>44579</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>44579</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>44579</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>44540</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>44911</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>44911</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>44540</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>44911</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61486,7 +61486,7 @@
         <v>44540</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>45351</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61642,7 +61642,7 @@
         <v>44911</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>45299</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>44540</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61871,7 +61871,7 @@
         <v>45351</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61949,7 +61949,7 @@
         <v>44540</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62027,7 +62027,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62105,7 +62105,7 @@
         <v>44501</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62178,7 +62178,7 @@
         <v>45779</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62251,7 +62251,7 @@
         <v>46035</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62329,7 +62329,7 @@
         <v>46177</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>46203</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45727</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>44867</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45203</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>44564</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45902</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45665</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45237</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45378</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44473</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44787</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44505</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45432</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45763</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45534</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45162</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45397</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45832</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45646</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44943</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45988</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45203</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44589</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45384</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45728</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45012</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44936</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>46280</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45106</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45323</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44512</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44735</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44830</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44629</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44475</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44488</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44719</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44580</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44552</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44886</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44750</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44552</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44776</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44824</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44735</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44745</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44624</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44543</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44505</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44676</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44719</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44780</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44780</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44511</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44846</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44711</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44861</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44780</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44602</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44868</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44629</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44616</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44649</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44538</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44819</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44806</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44526</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44616</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44719</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44644</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44826</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44683</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44679</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44686</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44518</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44698</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44829</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45740</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45740</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44546</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45425</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44825</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45278</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45306</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45621</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45050</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45050</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45720</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45747</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45266</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45266</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44745</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44512</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45278</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45278</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45171</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44709</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45425</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44881</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45113</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44830</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45988</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45988</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44606</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45173</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45231</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44823</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45988</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45631</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44627</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45238</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45005</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45791</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>45372</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45790</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>46006</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45790</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46010</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45107</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45791</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45790</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44852</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45226</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45617</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45888</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45888</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45331</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45558</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45834</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45454</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44487</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45890</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45893</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45893</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45893</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45893</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45699</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45729</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44720</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44763</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45790</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45790</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45790</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44911</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>46030</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>46030</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45898</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45398</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45888</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45418</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>46034</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>46037</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45902</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45374</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>45374</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>46041</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>46041</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45904</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>45676</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44538</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45910</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45910</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>46043</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45239</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45796</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>45707</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>46045</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45912</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>46045</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>46045</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45912</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45323</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>45638</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>46046</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46046</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45506</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45799</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45740</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45800</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45460</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45222</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>46055</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45807</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45264</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45615</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>46055</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44881</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45924</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45924</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45925</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45189</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>46058</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45516</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45699</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45728</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45113</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>46059</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45589</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45931</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44823</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>46065</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>44945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45711</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>45811</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44993</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>44924</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>44490</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45938</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45937</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>45943</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>46072</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>46073</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45811</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45944</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45945</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>44853</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45582</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45811</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45503</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>46078</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45946</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45358</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45630</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44635</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44872</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>45949</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>46079</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>46079</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45771</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45659</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>46079</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45950</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44900</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>46050</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45082</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>46083</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45607</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>46083</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45251</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45471</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45471</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45411</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>46083</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46083</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>46083</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45146</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46086</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45403</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45813</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45575</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>46090</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45147</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45419</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45253</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>46087</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>44896</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44976</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>46090</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>46087</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46087</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45623</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45716</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>46090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45989</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45763</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45961</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44608</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>44609</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>46092</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45667</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45667</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45667</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44587</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45646</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45761</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>44564</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>46093</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>46094</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45646</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46093</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45817</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44734</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44629</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44993</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45212</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45608</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>44509</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>45975</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45055</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>46101</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>46101</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>46104</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45099</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45757</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>46105</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>45977</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45107</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>46108</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45012</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45980</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45156</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45982</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>46111</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45983</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45982</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46111</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44550</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45988</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45988</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45989</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45825</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>46119</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45989</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>46119</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45988</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>45989</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45988</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>46122</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45993</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45993</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>45582</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>45995</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45995</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45729</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45831</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>45831</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45831</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45148</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45113</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45832</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>44985</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45453</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45208</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44994</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>46134</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45835</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>46134</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44880</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45278</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45387</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45356</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>45779</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>45343</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44523</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45706</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45189</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>45685</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32096,7 +32096,7 @@
         <v>45727</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>45334</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45245</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45874</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>46139</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45711</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44879</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45168</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45832</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45807</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45807</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45239</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44572</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45841</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>44936</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45912</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45874</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45932</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45089</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45842</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45609</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45391</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>45358</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>45735</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33858,7 +33858,7 @@
         <v>45728</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>45832</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45808</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44910</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45740</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45723</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45847</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45932</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45847</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>45621</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45847</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>45847</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45847</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>45301</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>46139</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>45905</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>45576</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>45204</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>44659</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>44762</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45012</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45278</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>44916</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>44943</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>45966</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44671</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>44607</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>45358</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>45771</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45880</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45282</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45191</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45714</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>45931</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45481</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45922</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45278</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45896</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>45874</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45387</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>46139</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45704</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45820</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45342</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45831</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>44580</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>44564</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45894</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45237</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45677</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45555</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45735</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45249</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45595</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45523</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>44663</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45471</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45324</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45847</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45005</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>44550</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45855</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45527</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45871</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45572</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>46142</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>46146</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45295</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45330</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45280</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>46149</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45176</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>46148</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45367</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44988</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45603</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45133</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45733</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45439</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>46155</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>45719</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>45261</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45837</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44777</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45379</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>46154</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45428</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>46198</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>45356</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45542</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45394</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45890</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45146</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>46059</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>45874</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45874</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>45825</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44678</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45603</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45310</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>45931</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45746</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45805</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45419</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45537</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45497</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>44881</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>46164</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>45337</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45769</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45258</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>46164</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>46167</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>45611</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>44509</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42293,7 +42293,7 @@
         <v>46170</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>46170</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>46170</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45525</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>46170</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>46170</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>46170</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>45719</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>46174</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45817</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45877</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45883</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>46170</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45425</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>46176</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>45603</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>46175</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44606</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>46177</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45006</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>46182</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45477</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45639</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45639</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44065,7 +44065,7 @@
         <v>45450</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>44813</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45728</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45107</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44960</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45457</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>46062</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45775</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45522</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45356</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45352</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45433</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45044</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>46191</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45222</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45428</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>44509</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45548</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>45439</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45313</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45021</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45271</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44509</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>46183</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>46203</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45266</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>45534</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45156</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>46105</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>46209</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>46209</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>44868</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>46209</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>46209</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45147</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45191</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>46209</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>46209</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>44552</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>45062</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45237</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47141,7 +47141,7 @@
         <v>45348</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>44909</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45771</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45564</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45609</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45078</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>46258</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>44824</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45559</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>44603</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>44501</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>46262</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>45012</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45127</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45720</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45583</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>45355</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>46266</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>46266</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>46266</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>45171</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>46269</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>46269</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45721</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45631</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45586</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45068</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45534</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>45070</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>44938</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>46273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>44745</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>46273</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>46232</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>46232</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>46232</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>46279</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>46233</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>46237</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>46237</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>46237</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50134,7 +50134,7 @@
         <v>46279</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>46237</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>46237</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>46279</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45368</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45454</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>46281</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45098</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>46281</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50796,7 +50796,7 @@
         <v>45524</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45597</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45597</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>46113</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>44861</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
         <v>46283</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>44763</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>45278</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45495</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>45575</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>45211</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>45211</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51687,7 +51687,7 @@
         <v>46283</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>46283</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>44487</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45516</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51984,7 +51984,7 @@
         <v>45516</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52057,7 +52057,7 @@
         <v>45237</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>45223</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45895</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52276,7 +52276,7 @@
         <v>45392</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>46287</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45910</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>46287</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45341</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>44819</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45989</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>46288</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52870,7 +52870,7 @@
         <v>45712</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52943,7 +52943,7 @@
         <v>45089</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>44876</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53089,7 +53089,7 @@
         <v>45457</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>46289</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>45547</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>45707</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>45156</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53454,7 +53454,7 @@
         <v>44880</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45635</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53600,7 +53600,7 @@
         <v>45253</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53673,7 +53673,7 @@
         <v>45233</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53746,7 +53746,7 @@
         <v>44881</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>44886</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>45180</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>46290</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>46290</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54111,7 +54111,7 @@
         <v>46295</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54184,7 +54184,7 @@
         <v>46290</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54257,7 +54257,7 @@
         <v>45474</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54330,7 +54330,7 @@
         <v>45569</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>44980</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>44952</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54549,7 +54549,7 @@
         <v>46251</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>46251</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54695,7 +54695,7 @@
         <v>46251</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54768,7 +54768,7 @@
         <v>46251</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>44812</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45095</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>44488</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>46255</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>45267</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55216,7 +55216,7 @@
         <v>46297</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>45397</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>44758</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45558</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55508,7 +55508,7 @@
         <v>45704</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45607</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>45740</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>45625</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>46253</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>46255</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55951,7 +55951,7 @@
         <v>45573</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>44581</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>44938</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56170,7 +56170,7 @@
         <v>45567</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>45107</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56316,7 +56316,7 @@
         <v>45527</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>44523</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>44994</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45685</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45728</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56681,7 +56681,7 @@
         <v>45106</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>45700</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>44929</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45426</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45229</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45191</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>45191</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>44959</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45237</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>44921</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>45720</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45692</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45692</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>44679</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45063</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45420</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
         <v>44973</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>45517</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45681</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58073,7 +58073,7 @@
         <v>45385</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58146,7 +58146,7 @@
         <v>45491</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58219,7 +58219,7 @@
         <v>45441</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>45075</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>44671</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45063</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45707</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>45040</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45365</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45281</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>45098</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45098</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58949,7 +58949,7 @@
         <v>45386</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>44509</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         <v>44998</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>44574</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59246,7 +59246,7 @@
         <v>45361</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>45314</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>45057</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59465,7 +59465,7 @@
         <v>44868</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59538,7 +59538,7 @@
         <v>45769</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45149</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59689,7 +59689,7 @@
         <v>45273</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45677</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45040</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>45393</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>44623</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60054,7 +60054,7 @@
         <v>45194</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>45672</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60200,7 +60200,7 @@
         <v>44489</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>45380</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>45783</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45369</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45427</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45555</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45784</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>45681</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>45646</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60857,7 +60857,7 @@
         <v>45736</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60930,7 +60930,7 @@
         <v>45720</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>44579</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
         <v>44540</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>44911</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>44911</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>44540</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>44911</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61476,7 +61476,7 @@
         <v>44540</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45351</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61632,7 +61632,7 @@
         <v>44911</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61710,7 +61710,7 @@
         <v>45299</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>44579</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>44540</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45351</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62017,7 +62017,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62095,7 +62095,7 @@
         <v>44579</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>44540</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62251,7 +62251,7 @@
         <v>44501</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45779</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62397,7 +62397,7 @@
         <v>46035</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62475,7 +62475,7 @@
         <v>46177</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62553,7 +62553,7 @@
         <v>46203</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45727</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>44867</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45203</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>44564</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45902</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45665</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>45237</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45460</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45378</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44473</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44787</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44505</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45432</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45763</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45534</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45162</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45397</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45912</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45832</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45646</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>44943</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45988</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45203</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44589</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45384</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45728</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45012</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44936</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>46280</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45106</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45323</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45644</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44512</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44735</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44830</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44629</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44475</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44488</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44719</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44580</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44552</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44886</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44750</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44552</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44776</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44824</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44735</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44745</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44494</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44624</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44543</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44505</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44676</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44719</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44780</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44780</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44511</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44846</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44840</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44711</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44861</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44780</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44607</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44602</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44868</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44629</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44616</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44649</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44538</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44819</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44806</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44526</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44616</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44719</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44644</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44826</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44683</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44679</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44686</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44518</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44698</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44829</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45740</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45740</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44546</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45425</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44825</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>45278</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45306</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45572</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45621</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45050</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45050</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45720</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45747</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45266</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45266</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44745</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44512</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45278</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>45278</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45171</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44709</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45425</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44881</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45113</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44830</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45988</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45988</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44606</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45173</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45231</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44823</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45988</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45631</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44627</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45238</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45005</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45791</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>45372</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45790</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>46006</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45790</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46010</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45107</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45791</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45790</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44852</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45226</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45617</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45888</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45888</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45331</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45558</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45834</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45454</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44487</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45890</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45893</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45893</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45893</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45893</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>45699</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45729</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44720</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>44763</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45790</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45790</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45790</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44911</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>46030</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>46030</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45898</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45901</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45398</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45888</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45418</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>46034</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>46037</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45902</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45374</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>45374</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>46041</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>46041</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45904</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>45904</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>45676</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44538</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45910</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45910</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>46043</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>45239</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45796</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>45707</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>46045</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>45912</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>46045</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>46045</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>45912</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45323</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>45638</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>46046</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46046</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>45506</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45799</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45740</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45800</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45460</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45222</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>46055</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45807</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45264</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45615</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>46055</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>44881</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         <v>45924</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45924</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45925</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45189</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>46058</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45516</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45699</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45728</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45113</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>46059</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45589</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>45931</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44823</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>46065</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>44945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45711</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20965,7 +20965,7 @@
         <v>45811</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44993</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>44924</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>44490</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45938</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>45937</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>45943</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>46072</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>46073</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45520</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>45811</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
         <v>45944</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21841,7 +21841,7 @@
         <v>45945</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21914,7 +21914,7 @@
         <v>44853</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>45582</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45811</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22138,7 +22138,7 @@
         <v>45503</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>46078</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>45946</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45358</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45630</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44635</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44872</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
         <v>45949</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>46079</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>46079</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>45771</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45659</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>46079</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45950</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44900</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>46050</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>45082</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>46083</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>45607</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>46083</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45251</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45471</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45471</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45411</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>46083</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>46083</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>46083</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45146</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46086</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45403</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45813</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45575</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>46090</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45147</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45419</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45253</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>46087</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>44896</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44976</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>46090</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>46087</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46087</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45623</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45716</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>46090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45989</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45763</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45961</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44608</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>44609</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>46092</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45667</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45667</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45667</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44587</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45646</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45761</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>44564</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>46093</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>46094</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45646</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46093</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45817</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44734</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44629</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44993</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45212</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45608</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>44509</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>45975</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45055</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>46101</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>46101</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>46104</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45975</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45099</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45757</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>46105</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>45977</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45107</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>46108</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45012</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45980</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45156</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45982</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>46111</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45983</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45982</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46111</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44550</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
         <v>45988</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45988</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45989</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45825</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>46119</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45989</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>46119</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45988</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>45989</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45988</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>46122</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45993</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45993</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>45582</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>45995</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45995</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45729</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45831</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>45831</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45831</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45148</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45113</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45832</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>44985</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45453</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45208</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44994</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>46134</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45835</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>46134</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44880</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45278</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45387</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45356</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>45779</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>45343</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44523</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
         <v>45706</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45189</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>45685</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32096,7 +32096,7 @@
         <v>45727</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
         <v>45334</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45245</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45874</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>46139</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45711</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44879</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>45168</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>45832</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>45807</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45807</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45239</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44572</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45841</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>44936</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45912</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45874</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45932</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45089</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45842</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45609</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45391</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>45358</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>45735</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33858,7 +33858,7 @@
         <v>45728</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>45832</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45808</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44910</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>45740</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45723</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45847</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45932</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45847</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>45621</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45847</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>45847</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45847</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>45301</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34895,7 +34895,7 @@
         <v>46139</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>45905</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>45576</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>45204</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>44659</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>44762</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45012</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45278</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>44916</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>44943</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>45966</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44671</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>44607</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>45358</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>45771</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>45880</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>45282</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45191</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45714</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>45931</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45481</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45922</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45278</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45896</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>45874</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45387</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>46139</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45704</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45820</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45342</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45831</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>44580</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>44564</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45894</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45237</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45677</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45555</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45735</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45249</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45595</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45523</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>44663</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45471</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45324</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45847</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45005</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>44550</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45855</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45527</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45871</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45572</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>46142</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>46146</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45295</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45330</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45280</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>46149</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>45176</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>46148</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45367</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44988</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45603</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45133</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45733</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45439</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>46155</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>45719</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>45261</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45837</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44777</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45379</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>46154</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45428</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>46198</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>45356</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45542</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45394</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45890</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45146</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>46059</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>45874</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40823,7 +40823,7 @@
         <v>45874</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>45825</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>44678</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45603</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45310</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>45931</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45746</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>45805</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45419</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45537</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>45497</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>44881</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41709,7 +41709,7 @@
         <v>46164</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>45337</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45769</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45258</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42001,7 +42001,7 @@
         <v>46164</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>46167</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>45611</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42220,7 +42220,7 @@
         <v>44509</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42293,7 +42293,7 @@
         <v>46170</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>46170</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>46170</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>45525</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>46170</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>46170</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>46170</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>45719</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>46174</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45817</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>45877</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45883</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>46170</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45425</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>46176</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>45603</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>46175</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44606</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>46177</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45006</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>46182</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45477</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45639</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45639</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44065,7 +44065,7 @@
         <v>45450</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>44813</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45728</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45107</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44960</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45457</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>46062</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45775</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45522</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45356</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45352</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45433</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45044</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>46191</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45222</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45428</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>44509</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45548</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>45439</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45313</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45021</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45271</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44509</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>46183</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>46203</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45266</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>45534</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45156</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>46105</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>46209</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>46209</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>44868</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>46209</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>46209</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45147</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45191</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>46209</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>46209</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>44552</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>45062</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45237</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47141,7 +47141,7 @@
         <v>45348</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>44909</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45771</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45564</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45609</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45078</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>46258</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>44824</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45559</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>44603</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>44501</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>46262</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>45012</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45127</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45720</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45583</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>45355</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>46266</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>46266</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>46266</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>45171</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>46269</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>46269</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45721</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45631</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45586</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45068</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45534</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>45070</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>44938</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>46273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>44745</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>46273</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>46232</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>46232</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>46232</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>46279</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>46233</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>46237</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>46237</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>46237</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50134,7 +50134,7 @@
         <v>46279</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>46237</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>46237</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>46279</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45368</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45454</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>46281</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45098</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>46281</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50796,7 +50796,7 @@
         <v>45524</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45597</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45597</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>46113</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>44861</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
         <v>46283</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>44763</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>45278</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45495</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51463,7 +51463,7 @@
         <v>45575</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>45211</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>45211</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51687,7 +51687,7 @@
         <v>46283</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>46283</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>44487</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45516</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51984,7 +51984,7 @@
         <v>45516</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52057,7 +52057,7 @@
         <v>45237</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>45223</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45895</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52276,7 +52276,7 @@
         <v>45392</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>46287</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45910</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>46287</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>45341</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>44819</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45989</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>46288</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52870,7 +52870,7 @@
         <v>45712</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52943,7 +52943,7 @@
         <v>45089</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>44876</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53089,7 +53089,7 @@
         <v>45457</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>46289</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>45547</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53308,7 +53308,7 @@
         <v>45707</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>45156</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53454,7 +53454,7 @@
         <v>44880</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45635</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53600,7 +53600,7 @@
         <v>45253</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53673,7 +53673,7 @@
         <v>45233</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53746,7 +53746,7 @@
         <v>44881</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>44886</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>45180</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>46290</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>46290</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54111,7 +54111,7 @@
         <v>46295</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54184,7 +54184,7 @@
         <v>46290</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54257,7 +54257,7 @@
         <v>45474</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54330,7 +54330,7 @@
         <v>45569</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54403,7 +54403,7 @@
         <v>44980</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>44952</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54549,7 +54549,7 @@
         <v>46251</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54622,7 +54622,7 @@
         <v>46251</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54695,7 +54695,7 @@
         <v>46251</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54768,7 +54768,7 @@
         <v>46251</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>44812</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45095</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>44488</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55065,7 +55065,7 @@
         <v>46255</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>45267</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55216,7 +55216,7 @@
         <v>46297</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>45397</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>44758</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55435,7 +55435,7 @@
         <v>45558</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55508,7 +55508,7 @@
         <v>45704</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45607</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>45740</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>45625</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>46253</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>46255</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55951,7 +55951,7 @@
         <v>45573</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>44581</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>44938</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56170,7 +56170,7 @@
         <v>45567</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>45107</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56316,7 +56316,7 @@
         <v>45527</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>44523</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>44994</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45685</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
         <v>45728</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56681,7 +56681,7 @@
         <v>45106</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>45700</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>44929</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45426</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45229</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45191</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57119,7 +57119,7 @@
         <v>45191</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>44959</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45237</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>44921</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>45720</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45692</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45692</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>44679</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45063</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45420</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
         <v>44973</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>45517</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>45681</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58073,7 +58073,7 @@
         <v>45385</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58146,7 +58146,7 @@
         <v>45491</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58219,7 +58219,7 @@
         <v>45441</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>45075</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>44671</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45063</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45707</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>45040</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45365</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45281</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>45098</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45098</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58949,7 +58949,7 @@
         <v>45386</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>44509</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         <v>44998</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>44574</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59246,7 +59246,7 @@
         <v>45361</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>45314</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>45057</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59465,7 +59465,7 @@
         <v>44868</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59538,7 +59538,7 @@
         <v>45769</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45149</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59689,7 +59689,7 @@
         <v>45273</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45677</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45040</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>45393</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>44623</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60054,7 +60054,7 @@
         <v>45194</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>45672</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60200,7 +60200,7 @@
         <v>44489</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>45380</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>45783</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45369</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45427</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45555</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45784</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>45681</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>45646</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60857,7 +60857,7 @@
         <v>45736</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60930,7 +60930,7 @@
         <v>45720</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>44579</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
         <v>44540</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61164,7 +61164,7 @@
         <v>44911</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>44911</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>44540</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>44911</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61476,7 +61476,7 @@
         <v>44540</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45351</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61632,7 +61632,7 @@
         <v>44911</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61710,7 +61710,7 @@
         <v>45299</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>44579</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>44540</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45351</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62017,7 +62017,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62095,7 +62095,7 @@
         <v>44579</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>44540</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62251,7 +62251,7 @@
         <v>44501</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45779</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62397,7 +62397,7 @@
         <v>46035</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62475,7 +62475,7 @@
         <v>46177</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62553,7 +62553,7 @@
         <v>46203</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44867</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>45727</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44564</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45203</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45460</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45902</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45303</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45665</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45378</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44787</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45763</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44505</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45323</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45384</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44943</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45203</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45534</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44589</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45432</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45162</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45397</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45646</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45728</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45988</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>44936</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45012</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45832</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>46304</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44735</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44488</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44552</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44580</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44886</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44552</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44581</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44776</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44824</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44735</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44745</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44494</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44624</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44543</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44505</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44711</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44526</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44861</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44676</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44780</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44616</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44629</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44719</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44719</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44644</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44780</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44780</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44538</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44607</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44602</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44819</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44511</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44868</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44629</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44826</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44616</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44806</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44557</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44649</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44683</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44550</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44686</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44518</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44698</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44627</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44813</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44936</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45156</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>44820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45107</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44998</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44823</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45229</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44829</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45367</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44881</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45457</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45771</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>44880</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45609</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45078</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44825</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45747</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45089</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45720</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45392</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45385</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45720</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45358</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45428</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45062</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44487</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45712</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45740</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45278</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45522</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45548</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45356</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45099</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45495</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>45208</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44758</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45149</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>45471</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44487</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>45368</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>45063</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>45386</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45261</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45558</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>45454</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44509</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45127</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44868</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45667</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>44916</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45266</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45237</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>44546</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45070</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44550</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45356</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45331</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>45457</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45147</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44911</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44609</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45398</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44861</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45411</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45365</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>44606</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45324</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45883</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44976</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45278</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45055</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45573</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45356</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>44938</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45374</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45374</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45439</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44709</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45453</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45107</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45005</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45279</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44896</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44921</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45361</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44959</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45877</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45306</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45454</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45817</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>44945</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>45888</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45888</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45156</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45635</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>44881</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45425</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>45834</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45133</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45278</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45342</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45176</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45266</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>44881</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>44886</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45173</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>45890</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45893</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45893</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45893</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45893</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45895</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45418</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45677</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44509</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45589</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45337</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44512</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45902</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45107</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45667</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45712</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44734</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45888</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45901</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45603</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45516</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45253</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45204</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45558</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45420</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>45747</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45441</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45428</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45707</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45603</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45685</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45729</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45904</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45576</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45639</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45639</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44564</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>44993</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45631</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45904</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45050</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45050</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45348</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45524</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45901</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45908</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45355</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45607</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45314</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44509</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45148</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45113</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45113</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45075</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44876</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45380</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45910</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45910</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45527</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45194</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45912</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45282</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45534</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45491</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45912</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45547</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45582</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45044</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45723</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45646</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45784</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45369</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45783</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45915</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45393</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45719</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45191</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45343</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45736</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>45460</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>44627</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>45575</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45617</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45681</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>45427</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45555</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45790</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45790</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45146</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45790</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45720</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45534</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>44881</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>45924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>44580</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>44720</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45231</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45790</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45790</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45233</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45334</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45790</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>45924</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>45098</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>45012</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45925</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45667</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45089</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45569</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45791</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45791</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45791</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>44603</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44550</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45707</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45796</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>44574</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45931</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45439</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45323</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>44943</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45564</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>45222</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44985</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45625</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>44659</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45506</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45638</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>44581</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>44678</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44607</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45239</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45146</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45711</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44587</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44606</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45707</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45799</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45800</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44745</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45238</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>45426</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>45938</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>45559</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45621</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45313</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>45107</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44679</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45520</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45156</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45397</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>45168</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45095</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45358</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45582</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>44872</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45503</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45615</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45630</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>44994</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45807</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45603</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45607</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45943</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45811</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>44635</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45811</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45068</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45944</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45098</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45575</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>44489</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45771</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45945</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45946</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45811</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45057</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45419</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45266</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45813</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44663</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45757</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45716</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45818</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45623</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45646</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45763</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45704</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45949</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45761</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45950</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45237</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45646</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45817</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45147</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45006</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45583</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45222</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45825</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>45567</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>45471</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45831</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44763</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45831</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45831</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45237</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45880</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45832</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45769</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45171</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45211</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45659</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45212</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45189</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>44823</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45961</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>44509</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44993</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45681</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45191</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>45835</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>44973</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45699</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45841</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45729</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45267</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45842</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>45223</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45517</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>45672</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>45832</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>45358</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45847</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45847</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45278</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45278</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45847</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45295</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45847</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45699</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45847</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45278</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45808</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45180</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45733</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45728</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45278</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45189</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45005</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>44853</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45113</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45113</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45352</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45977</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45330</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45692</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45692</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44564</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>44988</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45258</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45975</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45975</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45012</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45874</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45021</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45874</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45677</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45871</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>44938</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45980</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>45775</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>44830</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45171</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45537</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45982</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45746</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45264</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45310</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45769</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>44880</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>44490</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44852</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45711</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45982</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45676</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45239</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>44868</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>45497</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45281</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>45736</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>45728</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>44623</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>45700</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>44538</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45527</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45586</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45253</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45525</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>46101</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>46101</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45301</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45720</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>44924</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>46105</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45728</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>46104</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45211</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45983</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>44629</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45191</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45082</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45611</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45249</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45740</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45740</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>46106</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45988</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45721</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45988</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>44812</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>46111</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45621</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45988</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>45597</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>46111</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>46108</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>45988</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45988</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43320,7 +43320,7 @@
         <v>45992</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45989</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45989</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45989</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>44900</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45226</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>44960</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45608</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45391</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45993</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>46119</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>46119</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45993</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>46122</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45995</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45995</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45450</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45040</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>44824</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45572</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>44745</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45271</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44763</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46134</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45419</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45988</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45988</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>44552</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>46134</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>46006</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>45988</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45988</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45063</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45387</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45403</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45931</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>44671</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>44762</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>45251</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>45831</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>44501</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>44909</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45874</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>46010</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45771</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>44671</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45516</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45516</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         <v>45481</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46912,7 +46912,7 @@
         <v>45894</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44572</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>44879</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>44523</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>44777</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45728</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45425</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45012</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>45704</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>45807</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45807</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>44488</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>45387</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45932</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>44910</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>46030</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45820</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45706</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45905</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>45779</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>46030</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>46030</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45966</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>46034</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>45597</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>45922</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45880</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45685</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45735</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45874</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45912</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>46139</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45425</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>46037</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>45572</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>46041</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>46041</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>44608</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>45040</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45855</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>44952</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>46139</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45237</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45555</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50134,7 +50134,7 @@
         <v>45631</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45106</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>46043</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45433</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45874</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45932</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>45471</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45832</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>46046</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50796,7 +50796,7 @@
         <v>46045</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45896</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>46046</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45372</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45740</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45727</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>46139</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45394</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45847</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>46045</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>46045</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51687,7 +51687,7 @@
         <v>45609</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45714</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45253</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51906,7 +51906,7 @@
         <v>45735</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51979,7 +51979,7 @@
         <v>46055</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46055</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>46058</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>45595</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>46059</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>46142</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>45280</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>46146</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>46065</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>46148</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46149</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52782,7 +52782,7 @@
         <v>46072</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>46073</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45379</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>46079</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>46079</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>46078</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53220,7 +53220,7 @@
         <v>46079</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>46154</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
         <v>46083</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>46083</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53512,7 +53512,7 @@
         <v>46083</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53585,7 +53585,7 @@
         <v>46083</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>46083</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>46050</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>46155</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45837</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53950,7 +53950,7 @@
         <v>46087</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54023,7 +54023,7 @@
         <v>46087</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54096,7 +54096,7 @@
         <v>46087</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>46198</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>46086</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45989</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>46059</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>45890</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54534,7 +54534,7 @@
         <v>46090</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>45542</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>45825</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54753,7 +54753,7 @@
         <v>46090</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>46090</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54899,7 +54899,7 @@
         <v>46093</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54972,7 +54972,7 @@
         <v>46092</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55045,7 +55045,7 @@
         <v>46093</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>46094</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55191,7 +55191,7 @@
         <v>45931</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55269,7 +55269,7 @@
         <v>46164</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55342,7 +55342,7 @@
         <v>45805</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>46164</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>46167</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>46170</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>46170</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55712,7 +55712,7 @@
         <v>46170</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55785,7 +55785,7 @@
         <v>46170</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55863,7 +55863,7 @@
         <v>46170</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>46170</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>46175</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>46174</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56160,7 +56160,7 @@
         <v>46176</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>46177</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56306,7 +56306,7 @@
         <v>46182</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56379,7 +56379,7 @@
         <v>46062</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>44509</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>46191</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>46203</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>46183</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>46206</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         <v>46209</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56890,7 +56890,7 @@
         <v>46209</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56963,7 +56963,7 @@
         <v>46209</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>46105</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57109,7 +57109,7 @@
         <v>46209</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>46209</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57255,7 +57255,7 @@
         <v>46209</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>46266</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>46266</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57474,7 +57474,7 @@
         <v>46266</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57547,7 +57547,7 @@
         <v>46269</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57620,7 +57620,7 @@
         <v>46269</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57693,7 +57693,7 @@
         <v>46273</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57766,7 +57766,7 @@
         <v>46273</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57839,7 +57839,7 @@
         <v>46233</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57912,7 +57912,7 @@
         <v>46232</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>46232</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>46232</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58131,7 +58131,7 @@
         <v>46279</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58204,7 +58204,7 @@
         <v>46279</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58277,7 +58277,7 @@
         <v>46237</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>46237</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58423,7 +58423,7 @@
         <v>46237</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>46279</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58569,7 +58569,7 @@
         <v>46237</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58642,7 +58642,7 @@
         <v>46237</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58715,7 +58715,7 @@
         <v>46113</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>46281</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>46281</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>46283</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59007,7 +59007,7 @@
         <v>46283</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59085,7 +59085,7 @@
         <v>46283</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>46287</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59236,7 +59236,7 @@
         <v>46287</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>45910</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59387,7 +59387,7 @@
         <v>45895</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>46288</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59538,7 +59538,7 @@
         <v>45989</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>44819</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45341</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59757,7 +59757,7 @@
         <v>46289</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>46290</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59903,7 +59903,7 @@
         <v>46290</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>46290</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60049,7 +60049,7 @@
         <v>46251</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>46251</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60200,7 +60200,7 @@
         <v>46251</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>46253</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>46251</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>46295</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>46255</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60570,7 +60570,7 @@
         <v>46297</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>46297</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>46300</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>46255</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>46258</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60935,7 +60935,7 @@
         <v>46304</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>46262</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>44579</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61159,7 +61159,7 @@
         <v>44579</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>44579</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61315,7 +61315,7 @@
         <v>44540</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>44911</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61471,7 +61471,7 @@
         <v>44911</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61549,7 +61549,7 @@
         <v>44540</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61627,7 +61627,7 @@
         <v>44911</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>44540</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>45351</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>44911</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45299</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62090,7 +62090,7 @@
         <v>45351</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>44540</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>44540</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>44501</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62397,7 +62397,7 @@
         <v>45779</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62470,7 +62470,7 @@
         <v>46035</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62548,7 +62548,7 @@
         <v>46177</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62626,7 +62626,7 @@
         <v>46203</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44867</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>45727</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44564</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45203</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45460</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45902</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45303</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45665</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45378</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44787</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45763</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>44505</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45323</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45384</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44943</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45203</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45534</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45912</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44589</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45432</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45162</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45397</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45646</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>45728</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45988</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>44936</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45012</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45841</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45832</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46280</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>46304</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44735</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44488</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44552</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44580</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44886</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44552</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44581</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44776</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44824</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44735</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44745</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44494</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44624</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44491</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44543</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44505</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44711</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44526</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44861</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44676</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44780</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44616</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44629</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>44719</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44719</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44644</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44780</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44780</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44538</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44607</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44602</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44819</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44511</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>44868</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44629</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44846</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44826</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44616</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44806</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44840</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44840</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44557</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44649</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44683</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44546</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44550</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44686</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44518</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44698</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44627</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44813</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44936</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>45156</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>44820</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45107</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44998</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44823</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45229</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44829</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45367</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>44881</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45457</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>44929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45771</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>44880</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>45609</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45078</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44825</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45747</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45089</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45720</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45392</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45385</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45720</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45358</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45428</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45062</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>44487</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45712</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45740</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45278</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45522</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45548</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45356</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45099</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45495</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>45208</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44758</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45149</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>45471</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44487</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>45368</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>45063</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>45386</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45261</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45558</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>45454</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44509</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45127</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>44868</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45667</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>44916</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45266</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45237</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>44546</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45070</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44550</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45356</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45331</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>45457</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45273</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45147</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44911</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44609</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45398</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44861</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45411</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45365</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>44606</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45191</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>45324</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45883</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44976</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45278</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>45055</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45573</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45356</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>44938</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45374</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45374</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45439</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44709</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45453</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45107</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45005</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45279</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44896</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44921</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45361</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45477</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44959</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45877</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45306</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45454</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>45817</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>44945</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>45888</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45888</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45156</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45635</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>44881</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45425</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>45834</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45133</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>45278</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45342</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45176</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45266</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>44881</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>44886</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45173</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>45890</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45893</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45893</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45893</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>45893</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45895</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45418</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45677</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44509</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45589</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45337</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44512</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45902</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45107</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45667</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>45712</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44734</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45888</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45901</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45603</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45516</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45253</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45204</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45558</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45420</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>45747</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45441</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45428</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45707</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45603</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45685</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45729</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45904</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45576</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45639</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45639</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44564</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>44993</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45631</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45904</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45050</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45050</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45348</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45524</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45901</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45908</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45355</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45607</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45314</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44509</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45148</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45113</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45113</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45075</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>44876</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45380</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45910</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45910</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45527</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45194</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45912</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45282</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45534</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45491</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45912</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45547</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45582</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45044</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45723</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45646</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45784</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45369</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45783</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45915</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45393</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45719</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45191</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45343</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45736</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>45460</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>44627</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>45575</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45617</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45681</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>45427</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45555</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45790</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45790</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45146</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45790</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45720</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45534</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>44881</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25768,7 +25768,7 @@
         <v>45924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>44580</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>44720</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45231</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45790</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45790</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45233</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>45334</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>45790</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>45924</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>45098</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>45012</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45925</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45667</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45089</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>45569</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45791</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45791</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45791</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>44603</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44550</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>45707</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>45796</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>44574</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>45931</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45439</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45323</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>44943</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45564</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>45222</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>44985</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45625</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>44659</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45506</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45638</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>44581</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>44678</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44607</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45239</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45146</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45711</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44587</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44606</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45707</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>45799</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45800</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>44745</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45238</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>45426</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         <v>45938</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29599,7 +29599,7 @@
         <v>45559</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45621</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45313</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>45107</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44679</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45520</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45156</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>45397</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>45168</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>45095</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45358</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45582</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>44872</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45503</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45615</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45630</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>44994</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45807</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45603</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45607</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45943</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45811</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>44635</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45811</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45068</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45944</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45098</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45575</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>44489</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45771</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45945</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45946</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45811</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45057</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45419</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45266</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45813</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44663</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45757</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45716</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45818</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45623</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45646</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45763</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45704</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45949</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45761</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45950</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45237</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45646</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45817</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45147</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45006</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45583</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45222</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45825</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>45567</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>45471</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45831</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44763</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45831</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45831</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45237</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45880</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45832</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45769</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45171</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45211</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45659</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45212</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45189</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>44823</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45961</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>44509</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44993</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45681</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45191</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>45835</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>44973</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45699</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45841</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45729</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45267</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45842</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>45223</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45517</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>45672</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>45832</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36126,7 +36126,7 @@
         <v>45358</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45847</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45847</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45278</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45278</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45847</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>45295</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>45847</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45699</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36798,7 +36798,7 @@
         <v>45847</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45278</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45808</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45180</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>45733</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45728</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45278</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45189</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>45005</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>44853</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45113</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45113</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45352</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45977</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45330</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45692</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45692</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44564</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>44988</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45258</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45975</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>45975</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45012</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45874</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45021</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>45874</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45677</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45871</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>44938</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45980</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>45775</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>44830</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45171</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45537</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45982</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45746</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45264</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45310</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45769</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>44880</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>44490</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44852</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45711</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>45098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45982</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45676</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45239</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>44868</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>45497</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45281</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>45736</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>45728</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>44623</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40672,7 +40672,7 @@
         <v>45700</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>44538</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45527</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40891,7 +40891,7 @@
         <v>45586</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45253</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45525</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>46101</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>46101</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45301</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45720</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>44924</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>46105</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45728</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>46104</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45211</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45983</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>44629</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45191</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45082</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45611</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45249</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45740</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>45740</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>46106</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>45988</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45721</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45988</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>44812</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>46111</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45621</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42877,7 +42877,7 @@
         <v>45988</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>45597</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>46111</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>46108</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>45988</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45988</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43320,7 +43320,7 @@
         <v>45992</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45989</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45989</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45989</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>44900</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45226</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>44960</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45608</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45391</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45993</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>46119</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>46119</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>45993</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>46122</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45995</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45995</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45450</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45040</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>44824</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45572</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>44745</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45271</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>44763</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46134</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45419</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45988</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45988</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>44552</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>46134</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>46006</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>45988</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45988</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45063</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45387</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45403</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45931</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>44671</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>44762</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>45251</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>45831</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>44501</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>44909</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45874</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>46010</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45771</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>44671</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45516</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>45516</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         <v>45481</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46912,7 +46912,7 @@
         <v>45894</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>44572</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>44879</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>44523</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>44777</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45728</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45425</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45012</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>45704</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>45807</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45807</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>44488</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>45387</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45932</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>44910</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>46030</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45820</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45706</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45905</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>45779</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>46030</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>46030</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45966</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>46034</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>45597</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>45922</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45880</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45685</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45735</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45874</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45912</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>46139</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45425</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>46037</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>45572</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>46041</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>46041</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>44608</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>45040</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45855</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>44952</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>46139</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45237</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45555</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50134,7 +50134,7 @@
         <v>45631</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45106</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>46043</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45433</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45874</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45932</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>45471</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45832</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>46046</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50796,7 +50796,7 @@
         <v>46045</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45896</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>46046</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45372</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45740</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45245</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45727</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>46139</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45394</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45847</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>46045</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51614,7 +51614,7 @@
         <v>46045</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51687,7 +51687,7 @@
         <v>45609</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45714</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45253</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51906,7 +51906,7 @@
         <v>45735</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51979,7 +51979,7 @@
         <v>46055</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46055</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>46058</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>45595</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>46059</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>46142</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>45280</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>46146</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>46065</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>46148</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46149</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52782,7 +52782,7 @@
         <v>46072</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>46073</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45379</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>46079</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>46079</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>46078</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53220,7 +53220,7 @@
         <v>46079</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>46154</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53366,7 +53366,7 @@
         <v>46083</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53439,7 +53439,7 @@
         <v>46083</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53512,7 +53512,7 @@
         <v>46083</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53585,7 +53585,7 @@
         <v>46083</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>46083</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>46050</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>46155</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45837</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53950,7 +53950,7 @@
         <v>46087</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54023,7 +54023,7 @@
         <v>46087</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54096,7 +54096,7 @@
         <v>46087</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>46198</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>46086</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45989</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>46059</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>45890</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54534,7 +54534,7 @@
         <v>46090</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>45542</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>45825</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54753,7 +54753,7 @@
         <v>46090</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>46090</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54899,7 +54899,7 @@
         <v>46093</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54972,7 +54972,7 @@
         <v>46092</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55045,7 +55045,7 @@
         <v>46093</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>46094</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55191,7 +55191,7 @@
         <v>45931</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55269,7 +55269,7 @@
         <v>46164</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55342,7 +55342,7 @@
         <v>45805</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>46164</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>46167</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>46170</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>46170</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55712,7 +55712,7 @@
         <v>46170</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55785,7 +55785,7 @@
         <v>46170</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55863,7 +55863,7 @@
         <v>46170</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>46170</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>46175</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>46174</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56160,7 +56160,7 @@
         <v>46176</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>46177</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56306,7 +56306,7 @@
         <v>46182</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56379,7 +56379,7 @@
         <v>46062</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>44509</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56525,7 +56525,7 @@
         <v>46191</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>46203</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>46183</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>46206</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56817,7 +56817,7 @@
         <v>46209</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56890,7 +56890,7 @@
         <v>46209</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56963,7 +56963,7 @@
         <v>46209</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57036,7 +57036,7 @@
         <v>46105</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57109,7 +57109,7 @@
         <v>46209</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>46209</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57255,7 +57255,7 @@
         <v>46209</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>46266</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>46266</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57474,7 +57474,7 @@
         <v>46266</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57547,7 +57547,7 @@
         <v>46269</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57620,7 +57620,7 @@
         <v>46269</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57693,7 +57693,7 @@
         <v>46273</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57766,7 +57766,7 @@
         <v>46273</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57839,7 +57839,7 @@
         <v>46233</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57912,7 +57912,7 @@
         <v>46232</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>46232</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58058,7 +58058,7 @@
         <v>46232</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58131,7 +58131,7 @@
         <v>46279</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58204,7 +58204,7 @@
         <v>46279</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58277,7 +58277,7 @@
         <v>46237</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58350,7 +58350,7 @@
         <v>46237</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58423,7 +58423,7 @@
         <v>46237</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58496,7 +58496,7 @@
         <v>46279</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58569,7 +58569,7 @@
         <v>46237</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58642,7 +58642,7 @@
         <v>46237</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58715,7 +58715,7 @@
         <v>46113</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>46281</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>46281</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>46283</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59007,7 +59007,7 @@
         <v>46283</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59085,7 +59085,7 @@
         <v>46283</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>46287</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59236,7 +59236,7 @@
         <v>46287</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>45910</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59387,7 +59387,7 @@
         <v>45895</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>46288</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59538,7 +59538,7 @@
         <v>45989</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>44819</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>45341</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59757,7 +59757,7 @@
         <v>46289</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>46290</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59903,7 +59903,7 @@
         <v>46290</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>46290</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60049,7 +60049,7 @@
         <v>46251</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60127,7 +60127,7 @@
         <v>46251</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60200,7 +60200,7 @@
         <v>46251</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>46253</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>46251</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>46295</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>46255</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60570,7 +60570,7 @@
         <v>46297</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>46297</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>46300</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>46255</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>46258</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60935,7 +60935,7 @@
         <v>46304</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>46262</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>44579</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61159,7 +61159,7 @@
         <v>44579</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>44579</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61315,7 +61315,7 @@
         <v>44540</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>44911</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61471,7 +61471,7 @@
         <v>44911</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61549,7 +61549,7 @@
         <v>44540</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61627,7 +61627,7 @@
         <v>44911</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>44540</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>45351</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>44911</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45299</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62090,7 +62090,7 @@
         <v>45351</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>44540</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62246,7 +62246,7 @@
         <v>44540</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>44501</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62397,7 +62397,7 @@
         <v>45779</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62470,7 +62470,7 @@
         <v>46035</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62548,7 +62548,7 @@
         <v>46177</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62626,7 +62626,7 @@
         <v>46203</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45727</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>44867</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45203</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>44564</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45665</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45460</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45902</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45378</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44787</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44505</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45432</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45763</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45534</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45162</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>44943</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45203</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45384</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45988</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45012</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45832</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>44936</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45323</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>46280</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45397</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45644</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>46304</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45646</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45728</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44735</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44830</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44629</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44488</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44580</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44552</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44886</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44552</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44776</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44824</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44735</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44745</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44494</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44602</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44491</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44624</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44543</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44505</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44676</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44719</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44780</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44780</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44511</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44846</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44840</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44557</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44861</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44780</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44607</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44602</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44629</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44616</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44649</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44550</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44538</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44806</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44526</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44616</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44719</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44644</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44826</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44683</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44679</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44686</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44518</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44698</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44829</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45740</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45425</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44546</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45278</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45306</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45572</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45050</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45050</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45266</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45720</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45747</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45266</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45425</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44745</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45171</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44512</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>45278</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45278</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44830</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>45231</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44823</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44709</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45631</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44627</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45238</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45005</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45747</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44606</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45372</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45736</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45617</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45107</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45331</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45558</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44852</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45226</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>45454</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44487</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44720</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>45699</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44763</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44911</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45729</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45398</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45374</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45374</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45676</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44538</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45460</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45506</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45222</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45264</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44881</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45173</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45189</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45699</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45728</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45113</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45516</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44823</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44945</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44490</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45711</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44993</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44924</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45589</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44853</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45082</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44635</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45659</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44900</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45251</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45147</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45253</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45471</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45471</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45716</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45411</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45146</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>44896</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45403</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44976</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44608</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44609</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>45667</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45667</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>45667</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44587</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44564</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44734</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44629</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44993</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45212</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45608</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44509</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45099</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>45012</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45156</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45107</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45609</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45735</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45728</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44910</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45740</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45932</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>44550</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>46139</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45905</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45966</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45771</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45880</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45582</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45888</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>45888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45888</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44606</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45834</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45714</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45890</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45729</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45931</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45893</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45893</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45893</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45893</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45895</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45481</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45148</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45922</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>45113</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45113</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45896</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45898</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44985</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45901</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45874</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45453</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45208</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>46139</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45704</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45820</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45888</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>44994</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45894</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45595</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45418</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45847</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44880</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45278</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45356</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45343</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45902</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45189</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45904</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45904</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45334</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45245</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45711</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45908</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45901</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45855</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45168</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45910</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45910</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45239</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45912</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45915</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>46142</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>44936</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45912</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>46146</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45089</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45391</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45280</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45723</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45621</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45301</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45576</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>46149</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45924</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45924</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45925</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>44659</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45012</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45278</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44916</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>44943</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44671</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46148</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44607</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45358</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45931</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45191</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45938</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45937</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45278</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45943</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45387</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>46155</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45944</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45945</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45342</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44580</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>45946</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44564</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45237</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45677</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45555</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45837</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45949</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45950</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>45379</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45249</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>46154</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>44663</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45880</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>46198</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>45471</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45324</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45542</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45005</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45961</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>45890</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>44550</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45527</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>46059</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45572</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45825</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45295</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45330</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45805</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45975</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45975</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>45367</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>45977</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>44988</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>45603</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>46164</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>45133</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45733</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45982</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>45439</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45719</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45261</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44777</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45983</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45982</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>45428</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>46164</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>46167</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45988</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45988</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45989</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45356</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45989</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45988</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45988</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45989</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45394</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45988</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45992</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45146</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45993</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>44678</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45603</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45995</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45419</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45995</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>44881</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45337</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>46170</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45258</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>46170</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45988</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45988</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>46170</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>46170</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>46170</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45988</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
         <v>45988</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>45611</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>44509</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>46006</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45525</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45719</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>46174</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>46010</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45425</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45603</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>46170</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45006</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45477</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45639</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45639</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45450</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>44813</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45728</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>46030</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>46030</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33858,7 +33858,7 @@
         <v>46030</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44960</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>46176</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>46175</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>46034</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>46037</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>46041</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>46041</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>46177</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45457</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>46043</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45775</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45522</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>46045</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45356</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45352</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>46045</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>46045</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46046</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46046</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>46182</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>45433</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>46055</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45044</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>46055</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45222</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45428</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>46058</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45548</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>46059</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45439</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45313</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>46065</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45021</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45271</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>44509</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>46073</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>46078</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>46079</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>46079</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>46079</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>45266</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>46062</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>46050</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45534</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>46083</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>46083</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45156</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>46083</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>46083</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>46083</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>46086</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>46090</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>46087</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>44868</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>46090</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>46087</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>46087</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>45147</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>46090</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45191</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45989</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>44552</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45062</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>46092</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>46093</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>46094</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>46093</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45237</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45348</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>44909</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45771</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45564</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46101</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46101</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46104</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45609</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46106</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45078</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>44824</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>46105</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45559</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>46191</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>46108</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>44603</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44509</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>44501</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>46111</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>45012</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>46111</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45127</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45720</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45583</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45355</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46119</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46119</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46122</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45171</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45721</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45631</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>45586</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>46183</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>46203</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45068</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45534</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>45070</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>44938</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>46134</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>44745</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>46134</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45387</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45779</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>44523</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45706</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45685</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45727</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45368</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>45454</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45874</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>46139</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>46206</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         <v>44879</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>45098</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>45832</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45524</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45597</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>45597</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>45807</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45807</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>44572</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44861</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45912</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45874</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45932</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>44763</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>45278</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45495</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45575</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45211</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45211</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46105</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>44487</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>46209</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46209</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45516</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45516</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>46209</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>46209</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>46209</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>46209</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45237</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45223</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45392</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45712</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45089</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>44876</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>45457</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>46273</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>45547</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46273</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45707</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45156</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>46232</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>44880</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>46232</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>45635</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45253</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>46232</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>46279</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>46233</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45233</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>46237</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>46237</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>46237</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>44881</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>44886</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45180</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>46279</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>45474</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45569</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>44980</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>46237</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>46237</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>46279</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>44952</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46281</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>46281</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>44812</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45095</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>46113</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>44488</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>46283</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45267</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>46283</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45397</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>46283</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44758</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45558</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45704</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45607</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45740</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45625</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>45573</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45895</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>44581</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>46287</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>44938</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         <v>45910</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45567</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>46287</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45527</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>44523</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45341</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49608,7 +49608,7 @@
         <v>44819</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45989</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>46288</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>44994</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45685</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45728</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>45106</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45700</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>44929</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>45426</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45229</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45191</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45191</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>44959</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>45237</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>46289</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>44921</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45720</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45692</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>45692</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>44679</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45063</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45420</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>44973</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45517</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45681</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45385</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>45491</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45441</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45075</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>44671</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>46290</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>46290</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46295</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>46290</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45707</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>45040</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45365</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45281</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45098</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45098</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45386</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>44509</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>44998</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>46251</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>44574</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45361</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45314</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>46251</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>46251</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>46251</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45057</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>44868</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45769</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45149</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>45273</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>45677</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45040</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>46297</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>45393</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>44623</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>46253</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45194</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>45672</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>44489</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45380</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>45783</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45369</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>46300</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>46297</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>46255</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54894,7 +54894,7 @@
         <v>45427</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45555</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45784</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>45681</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45646</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45736</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46255</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45720</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>46258</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>44881</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45791</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45790</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55785,7 +55785,7 @@
         <v>45790</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55863,7 +55863,7 @@
         <v>45791</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45791</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56014,7 +56014,7 @@
         <v>45790</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>45790</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56165,7 +56165,7 @@
         <v>45790</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>45790</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56321,7 +56321,7 @@
         <v>46304</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56394,7 +56394,7 @@
         <v>45239</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>45796</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>45707</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56613,7 +56613,7 @@
         <v>46262</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56686,7 +56686,7 @@
         <v>45323</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45638</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>45799</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>46266</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46266</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>45800</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57124,7 +57124,7 @@
         <v>46266</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45807</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57270,7 +57270,7 @@
         <v>45615</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45811</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>46308</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45520</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45811</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>46309</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45582</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45811</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45503</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57932,7 +57932,7 @@
         <v>45358</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45630</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58078,7 +58078,7 @@
         <v>44872</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45771</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58224,7 +58224,7 @@
         <v>45607</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45813</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45575</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58443,7 +58443,7 @@
         <v>45419</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>45623</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58589,7 +58589,7 @@
         <v>45763</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58662,7 +58662,7 @@
         <v>45646</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58735,7 +58735,7 @@
         <v>45761</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45646</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58881,7 +58881,7 @@
         <v>45817</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58954,7 +58954,7 @@
         <v>45818</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>46309</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         <v>45757</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>46269</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59246,7 +59246,7 @@
         <v>46310</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>46309</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>46309</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59465,7 +59465,7 @@
         <v>45825</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59538,7 +59538,7 @@
         <v>46269</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>46309</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>46311</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45831</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>45831</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45832</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60054,7 +60054,7 @@
         <v>45835</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60132,7 +60132,7 @@
         <v>45841</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>45842</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60278,7 +60278,7 @@
         <v>45358</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>45832</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60424,7 +60424,7 @@
         <v>45808</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45847</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60570,7 +60570,7 @@
         <v>45847</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45847</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>45847</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>45847</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>45871</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60935,7 +60935,7 @@
         <v>45874</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>45874</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>45310</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>45746</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61227,7 +61227,7 @@
         <v>45537</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61300,7 +61300,7 @@
         <v>45497</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61373,7 +61373,7 @@
         <v>45769</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         <v>45817</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>45877</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61592,7 +61592,7 @@
         <v>45883</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>44579</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61748,7 +61748,7 @@
         <v>44540</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>44911</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>44911</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>44911</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62138,7 +62138,7 @@
         <v>44540</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62216,7 +62216,7 @@
         <v>45351</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>44911</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45299</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62445,7 +62445,7 @@
         <v>44579</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62523,7 +62523,7 @@
         <v>44540</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62601,7 +62601,7 @@
         <v>45351</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62679,7 +62679,7 @@
         <v>44540</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>44579</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>44540</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>44501</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -62986,7 +62986,7 @@
         <v>45779</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>46035</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63137,7 +63137,7 @@
         <v>46177</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>46203</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45727</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>44867</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>45203</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>44564</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45665</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45460</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>45902</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45378</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>44673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44787</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44505</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45432</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45763</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45534</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45162</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>44943</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45912</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45203</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44589</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45384</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45988</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45012</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45832</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>44936</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45323</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>46280</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45397</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45644</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>46304</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45646</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45673</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45728</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44735</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44830</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44508</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44629</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44488</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44580</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44552</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44886</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44552</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44776</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44824</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44735</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44745</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44494</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44602</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44491</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44624</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44543</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44505</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44676</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44719</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44780</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44780</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44511</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>44846</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44840</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44557</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44711</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44861</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44780</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44607</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44607</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44602</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44868</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44629</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44616</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44649</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44550</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44538</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44819</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44806</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44526</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44616</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44719</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44644</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44826</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44683</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44679</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44686</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44518</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44698</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44627</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44829</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45740</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45425</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44546</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45278</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45306</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45572</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45050</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45050</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45266</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45720</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45747</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>45266</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45425</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45279</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44745</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45171</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45113</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44512</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>45278</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45278</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44830</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>45231</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44823</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44709</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45631</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44627</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45238</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45005</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45747</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44606</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45372</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45736</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45617</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45107</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45331</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45558</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44852</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45226</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>45454</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>44487</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>44720</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>45699</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44763</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44911</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>45729</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45398</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45374</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45374</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45676</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44538</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45460</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45506</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45222</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45264</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44881</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45173</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45189</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45699</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45728</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45113</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45516</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44823</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44945</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>44490</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45711</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>44993</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44924</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45589</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44853</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45082</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44635</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45659</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>44900</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45251</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45147</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>45253</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45471</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45471</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45716</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>45411</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16764,7 +16764,7 @@
         <v>45146</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>44896</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45403</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>44976</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44608</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44609</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>45667</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45667</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>45667</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44587</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44564</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44734</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44629</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>44993</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45212</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45608</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44509</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45099</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>45012</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45156</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45107</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45609</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45735</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45728</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44910</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45740</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>45932</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>44550</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>46139</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45905</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>44762</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45966</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45771</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>45880</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45582</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45888</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>45888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45888</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44606</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45834</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45714</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45890</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45729</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45931</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>45893</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>45893</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45893</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45893</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>45895</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45481</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45148</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45922</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>45113</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45113</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45896</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>45898</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44985</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>45901</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21106,7 +21106,7 @@
         <v>45874</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45453</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45208</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21325,7 +21325,7 @@
         <v>46139</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45704</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45820</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45831</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>45888</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>44994</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>45894</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>45595</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45418</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45847</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>44880</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>45278</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45356</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22347,7 +22347,7 @@
         <v>45343</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>45902</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>45189</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>45904</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45904</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45334</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45245</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45711</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45908</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45901</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45855</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45168</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45910</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45910</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45239</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45912</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45915</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>46142</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>44936</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45912</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>46146</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45089</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45391</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45280</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45723</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>45621</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45301</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45576</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>46149</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45924</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45924</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45925</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>44659</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45012</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45278</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44916</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>44943</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44671</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46148</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44607</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45358</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45931</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45282</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45191</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45938</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45937</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45278</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45943</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45387</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>46155</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45944</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45945</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45342</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44580</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>45946</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44564</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45237</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45677</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45555</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45837</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45949</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>45950</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>45379</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45249</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>46154</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>44663</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45880</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>46198</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>45471</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45324</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45542</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>45005</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45961</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>45890</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>44550</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45527</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>46059</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45572</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45825</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>45295</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>45330</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>45805</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45975</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>45176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45975</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>45367</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>45977</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>44988</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>45603</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>46164</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>45133</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45733</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45982</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>45439</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45719</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45261</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>44777</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45983</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45982</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>45428</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>46164</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>46167</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45988</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45988</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45989</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45356</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>45989</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45988</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45988</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30621,7 +30621,7 @@
         <v>45989</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45394</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>45988</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45992</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30913,7 +30913,7 @@
         <v>45146</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45993</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>44678</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45603</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31278,7 +31278,7 @@
         <v>45995</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>45419</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45995</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>44881</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>45337</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>46170</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45258</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>46170</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45988</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45988</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>46170</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>46170</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>46170</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32242,7 +32242,7 @@
         <v>45988</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
         <v>45988</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>45611</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>44509</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>46006</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45525</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45719</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>46174</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>46010</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45425</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>45603</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>46170</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45006</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>45477</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45639</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45639</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45450</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>44813</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33566,7 +33566,7 @@
         <v>45728</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45107</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>46030</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         <v>46030</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33858,7 +33858,7 @@
         <v>46030</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44960</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>46176</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>46175</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>46034</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>46037</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>46041</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>46041</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>46177</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34515,7 +34515,7 @@
         <v>45457</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>46043</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>45775</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45522</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>46045</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>45356</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45352</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>46045</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>46045</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>46046</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46046</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35318,7 +35318,7 @@
         <v>46182</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35391,7 +35391,7 @@
         <v>45433</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>46055</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45044</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>46055</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45222</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45428</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35829,7 +35829,7 @@
         <v>46058</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45548</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>46059</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45439</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45313</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>46065</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>45021</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45271</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>44509</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>46072</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>46073</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>46078</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>46079</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>46079</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>46079</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>45266</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>46062</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37070,7 +37070,7 @@
         <v>46050</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45534</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>46083</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>46083</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45156</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>46083</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>46083</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>46083</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>46086</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>46090</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>46087</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37878,7 +37878,7 @@
         <v>44868</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>46090</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38024,7 +38024,7 @@
         <v>46087</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38097,7 +38097,7 @@
         <v>46087</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>45147</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>46090</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45191</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45989</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>44552</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45062</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>46092</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>46093</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>46094</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>46093</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45237</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45348</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>44909</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45771</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>45564</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46101</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>46101</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>46104</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45609</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46106</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45078</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>44824</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>46105</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39849,7 +39849,7 @@
         <v>45559</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>46191</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>46108</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>44603</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44509</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>44501</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>46111</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>45012</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>46111</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>45127</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45720</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45583</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45355</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46119</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46119</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46122</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45171</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45721</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45631</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>45586</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>46183</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>46203</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>45068</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45534</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41611,7 +41611,7 @@
         <v>45070</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>44938</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>46134</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>44745</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>46134</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>45387</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45779</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>44523</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>45706</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45685</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45727</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45368</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>45454</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45874</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>46139</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>46206</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
         <v>44879</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>45098</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
         <v>45832</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45524</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>45597</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>45597</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>45807</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45807</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>44572</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>44861</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45912</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45874</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45932</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>44763</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>45278</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>45495</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45575</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45211</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45211</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>46105</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>44487</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>46209</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46209</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45516</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45516</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>46209</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>46209</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>46209</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>46209</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45237</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45223</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>45392</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45712</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45089</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>44876</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45354,7 +45354,7 @@
         <v>45457</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>46273</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45500,7 +45500,7 @@
         <v>45547</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>46273</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45646,7 +45646,7 @@
         <v>45707</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45156</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>46232</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>44880</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>46232</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>45635</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45253</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
         <v>46232</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>46279</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>46233</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46376,7 +46376,7 @@
         <v>45233</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>46237</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>46237</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46595,7 +46595,7 @@
         <v>46237</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>44881</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46741,7 +46741,7 @@
         <v>44886</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46814,7 +46814,7 @@
         <v>45180</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>46279</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>45474</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>45569</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>44980</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47179,7 +47179,7 @@
         <v>46237</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>46237</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>46279</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>44952</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46281</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>46281</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>44812</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45095</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>46113</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>44488</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>46283</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45267</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>46283</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45397</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>46283</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>44758</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45558</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45704</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45607</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45740</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45625</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>45573</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45895</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>44581</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>46287</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>44938</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         <v>45910</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45567</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>46287</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45527</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>44523</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49535,7 +49535,7 @@
         <v>45341</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49608,7 +49608,7 @@
         <v>44819</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45989</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>46288</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>44994</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45685</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45728</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>45106</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45700</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>44929</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>45426</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45229</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45191</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45191</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>44959</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>45237</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>46289</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>44921</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45720</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>45692</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>45692</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>44679</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45063</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45420</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>44973</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45517</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45681</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45385</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>45491</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45441</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>45075</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>44671</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>45063</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>46290</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>46290</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52100,7 +52100,7 @@
         <v>46295</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>46290</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45707</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>45040</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>45365</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45281</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45098</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45098</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45386</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>44509</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>44998</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>46251</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>44574</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>45361</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>45314</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>46251</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>46251</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>46251</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45057</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>44868</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45769</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45149</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>45273</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>45677</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45040</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>46297</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>45393</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>44623</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>46253</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45194</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>45672</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>44489</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45380</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>45783</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45369</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>46300</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>46297</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>46255</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54894,7 +54894,7 @@
         <v>45427</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>45555</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45784</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55113,7 +55113,7 @@
         <v>45681</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45646</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45736</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46255</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45720</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>46258</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55556,7 +55556,7 @@
         <v>44881</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45791</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55707,7 +55707,7 @@
         <v>45790</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55785,7 +55785,7 @@
         <v>45790</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55863,7 +55863,7 @@
         <v>45791</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45791</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56014,7 +56014,7 @@
         <v>45790</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>45790</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56165,7 +56165,7 @@
         <v>45790</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>45790</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56321,7 +56321,7 @@
         <v>46304</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56394,7 +56394,7 @@
         <v>45239</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>45796</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>45707</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56613,7 +56613,7 @@
         <v>46262</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56686,7 +56686,7 @@
         <v>45323</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45638</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>45799</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>46266</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>46266</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>45800</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57124,7 +57124,7 @@
         <v>46266</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45807</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57270,7 +57270,7 @@
         <v>45615</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45811</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>46308</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45520</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45811</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>46309</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>45582</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45811</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57859,7 +57859,7 @@
         <v>45503</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57932,7 +57932,7 @@
         <v>45358</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>45630</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58078,7 +58078,7 @@
         <v>44872</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58151,7 +58151,7 @@
         <v>45771</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58224,7 +58224,7 @@
         <v>45607</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58297,7 +58297,7 @@
         <v>45813</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45575</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58443,7 +58443,7 @@
         <v>45419</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>45623</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58589,7 +58589,7 @@
         <v>45763</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58662,7 +58662,7 @@
         <v>45646</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58735,7 +58735,7 @@
         <v>45761</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45646</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58881,7 +58881,7 @@
         <v>45817</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58954,7 +58954,7 @@
         <v>45818</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59027,7 +59027,7 @@
         <v>46309</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59100,7 +59100,7 @@
         <v>45757</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>46269</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59246,7 +59246,7 @@
         <v>46310</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>46309</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>46309</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59465,7 +59465,7 @@
         <v>45825</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59538,7 +59538,7 @@
         <v>46269</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59611,7 +59611,7 @@
         <v>46309</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59684,7 +59684,7 @@
         <v>46311</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45831</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>45831</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45832</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60054,7 +60054,7 @@
         <v>45835</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60132,7 +60132,7 @@
         <v>45841</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>45842</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60278,7 +60278,7 @@
         <v>45358</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>45832</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60424,7 +60424,7 @@
         <v>45808</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45847</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60570,7 +60570,7 @@
         <v>45847</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45847</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>45847</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>45847</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>45871</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60935,7 +60935,7 @@
         <v>45874</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>45874</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>45310</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>45746</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61227,7 +61227,7 @@
         <v>45537</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61300,7 +61300,7 @@
         <v>45497</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61373,7 +61373,7 @@
         <v>45769</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         <v>45817</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>45877</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61592,7 +61592,7 @@
         <v>45883</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>44579</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61748,7 +61748,7 @@
         <v>44540</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>44911</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61904,7 +61904,7 @@
         <v>44911</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>44911</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62138,7 +62138,7 @@
         <v>44540</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62216,7 +62216,7 @@
         <v>45351</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>44911</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45299</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62445,7 +62445,7 @@
         <v>44579</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62523,7 +62523,7 @@
         <v>44540</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62601,7 +62601,7 @@
         <v>45351</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62679,7 +62679,7 @@
         <v>44540</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>44579</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>44540</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>44501</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -62986,7 +62986,7 @@
         <v>45779</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>46035</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63137,7 +63137,7 @@
         <v>46177</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>46203</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44867</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>45727</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44564</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45203</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45902</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45460</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>46220</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>44673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45665</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45378</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44787</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44505</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45012</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45912</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45384</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45988</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45534</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>46280</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45644</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45397</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>45323</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45832</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45646</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46304</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44943</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>45432</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45763</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>45203</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>44589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45162</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44936</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44629</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44735</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44580</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44552</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44886</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44750</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44552</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44581</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44776</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44748</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44745</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44494</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44624</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44543</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44505</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44676</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44629</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44719</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44780</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44780</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44511</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44846</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44840</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44840</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44711</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44861</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44780</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44607</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44607</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44602</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44868</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44629</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44616</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44649</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44546</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44550</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44538</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44819</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44806</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44526</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44616</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44719</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44644</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44826</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44683</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44686</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45877</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44518</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44627</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45817</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45888</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45387</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44829</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45834</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45403</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45208</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45890</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44671</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45893</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45893</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45893</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45893</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45251</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45895</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44501</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45418</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45898</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44671</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45516</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45516</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44777</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45902</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45425</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45888</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45901</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45012</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45904</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45904</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45901</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45910</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45912</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45912</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45931</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>46164</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45597</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>45915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>46164</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45425</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45924</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44608</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45040</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45924</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44952</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>46167</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45925</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45237</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45555</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45631</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45106</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45433</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45367</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>46170</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>46170</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45931</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45471</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>46170</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>46170</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>46170</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>46175</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45372</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45245</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45394</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>44825</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45937</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45107</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>46174</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44998</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45943</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45392</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45385</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45428</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44823</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45944</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>46176</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>46177</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45471</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45457</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45945</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45386</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44929</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45261</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45558</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45454</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45946</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44868</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45237</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45070</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44550</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45949</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45950</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45457</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45523</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45358</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45062</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>44523</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46182</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45522</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45880</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45495</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45149</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45127</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>44911</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45667</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44916</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45266</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45961</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44546</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>46062</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44861</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45147</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45411</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45365</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45324</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45055</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45356</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45719</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44509</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44709</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45005</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>46191</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45977</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45278</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45279</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45975</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45975</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45474</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>44921</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45361</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45573</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45477</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44959</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45156</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45980</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>46203</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>46183</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>44938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45635</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45982</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45982</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45133</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46206</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45278</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45176</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>44881</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>44886</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45173</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45439</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45983</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>46209</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45988</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>46209</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>46209</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45988</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45677</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>46105</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>46209</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45337</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45988</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>46209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45988</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45988</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>46209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45107</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45667</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>45992</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45989</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45712</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44734</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45453</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45989</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45989</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45107</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45993</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45993</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45747</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45441</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>45707</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45603</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>45995</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45685</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45995</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45576</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45639</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45639</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45380</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45988</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45988</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>46006</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45988</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45988</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45646</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45784</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>45369</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>46233</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>46232</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45783</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>46232</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>46232</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>46279</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>46279</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>46010</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46237</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45736</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>46237</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>46237</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45681</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>46279</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>46237</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>46237</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45427</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45555</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45790</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45790</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>46281</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45790</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45720</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>44881</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45790</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45790</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45790</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45306</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>46030</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46281</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46030</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46030</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>46034</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>46283</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45791</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45454</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45791</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45791</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45707</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>45796</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>46283</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>46283</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>46037</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45323</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>46287</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>46041</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>46287</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>46041</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45910</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45895</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>46043</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45638</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45989</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>46046</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>46045</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>46046</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>44819</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>46045</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>46045</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45341</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45799</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45800</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>46055</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>46055</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>45520</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>44881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>46058</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>46289</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>45358</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>45582</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44872</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45503</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45615</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45630</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45807</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>46290</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45607</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45811</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45811</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>46059</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45575</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45771</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45811</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45419</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46290</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>46290</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45813</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>46065</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45757</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45818</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45623</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45646</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45763</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45761</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45817</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>46072</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>46251</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45342</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>46251</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>46251</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>46073</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>46253</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>46079</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>46078</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>46083</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>46083</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>46251</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>46083</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>46083</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>46083</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45831</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45831</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>45831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>46295</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>46050</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45832</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>46255</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>46087</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>46087</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>46087</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>46086</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45989</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>46090</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>46090</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45835</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46090</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46093</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>46092</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35454,7 +35454,7 @@
         <v>46093</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>46297</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35600,7 +35600,7 @@
         <v>46297</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>46300</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>46094</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45841</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45842</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>46255</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>46101</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>46101</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45832</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45358</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46105</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>46104</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>45847</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>45847</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45847</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44509</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45589</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45847</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45808</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>44512</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>46106</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>46258</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>46111</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46111</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>46108</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>46304</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45516</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>46119</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45253</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>46119</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45874</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45420</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45874</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>46122</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>45428</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>45871</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>45729</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45537</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45746</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>44564</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45310</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45769</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44993</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45631</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45497</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45050</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45050</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45524</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>46134</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44606</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46134</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>45883</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45148</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45113</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45113</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45075</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>44876</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45194</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45534</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45491</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>45547</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>45931</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>46262</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44762</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45831</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>46310</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45874</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>46266</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45771</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>46309</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>46309</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>45481</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45894</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45343</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46266</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>44572</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>44879</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44523</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>46266</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44627</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45728</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45704</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>45575</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45617</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45807</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45807</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45387</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>46309</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45932</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>44910</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>46309</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>46311</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45820</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>46314</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45706</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45905</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45779</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45966</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>44580</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45740</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44720</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45231</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>46269</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45233</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>46113</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45098</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>46309</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>46269</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>45012</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45922</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>45880</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45735</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45874</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45912</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>46314</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>46314</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46139</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>45569</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>45855</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>46273</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46139</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45874</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45685</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>45932</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>46308</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>44574</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45896</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45740</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>45727</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>46273</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>46139</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>44943</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>46079</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45564</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45847</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45222</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45609</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45714</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45802,7 +45802,7 @@
         <v>44985</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>44659</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>44678</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>46317</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>45735</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>46317</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>46315</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45595</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>46142</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45707</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>46317</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45280</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>46146</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>44980</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>46148</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>44745</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>45238</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>45426</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>46149</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45559</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44679</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45156</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45397</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45168</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>45095</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>45379</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>44994</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45603</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>46154</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45068</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>46155</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>45266</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45837</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45716</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46198</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>46059</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45890</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45542</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45825</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45237</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45006</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45567</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>45471</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45189</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>44509</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>44993</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49160,7 +49160,7 @@
         <v>44973</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         <v>45267</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45672</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45699</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45189</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45005</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45113</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45113</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45692</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45692</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>44564</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45012</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45021</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45677</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45775</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>44830</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45171</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>44880</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45711</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45676</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>44538</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45586</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45253</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45525</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>45720</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>44629</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45191</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45082</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>45611</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45249</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>45721</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>44812</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45226</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>44813</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>44936</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45229</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51793,7 +51793,7 @@
         <v>44881</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45771</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>44880</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45609</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45078</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45747</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45089</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>45740</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45278</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45548</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45356</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45099</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>44758</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
         <v>45368</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45063</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>44509</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45356</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45331</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53132,7 +53132,7 @@
         <v>45273</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45398</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>44976</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45374</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45374</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45425</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45266</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>44994</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>45603</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45204</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45558</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>45348</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>45355</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>45607</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45314</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>44509</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45527</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45282</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>45582</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45044</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>45723</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45393</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45719</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45191</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45460</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45146</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45534</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45334</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45667</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>45089</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>44603</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>44550</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45439</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45625</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45506</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>44581</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>44607</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45146</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45711</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>44587</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>44606</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56213,7 +56213,7 @@
         <v>45621</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56286,7 +56286,7 @@
         <v>45313</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56359,7 +56359,7 @@
         <v>45107</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>44635</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56505,7 +56505,7 @@
         <v>45098</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56578,7 +56578,7 @@
         <v>44663</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>45704</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56724,7 +56724,7 @@
         <v>45147</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56797,7 +56797,7 @@
         <v>45583</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45222</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56943,7 +56943,7 @@
         <v>44763</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         <v>45237</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45769</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45171</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45211</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57318,7 +57318,7 @@
         <v>45659</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45212</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>44823</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57537,7 +57537,7 @@
         <v>45681</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
         <v>45191</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45699</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57761,7 +57761,7 @@
         <v>45729</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57839,7 +57839,7 @@
         <v>45223</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57912,7 +57912,7 @@
         <v>45517</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45278</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45278</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>45295</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58214,7 +58214,7 @@
         <v>45278</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>45180</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>45733</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45728</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45278</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>44853</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45352</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45330</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>44988</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45258</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58949,7 +58949,7 @@
         <v>44938</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>45264</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59095,7 +59095,7 @@
         <v>44852</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45098</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59241,7 +59241,7 @@
         <v>45239</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>44868</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59387,7 +59387,7 @@
         <v>45281</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45736</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45728</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>44623</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45700</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>45527</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45301</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>44924</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45728</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>45211</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60117,7 +60117,7 @@
         <v>45740</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>45740</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>45621</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>45597</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>44900</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>44960</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45608</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45391</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>45450</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>45040</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>44824</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60935,7 +60935,7 @@
         <v>45572</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>44745</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>45271</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>44763</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61232,7 +61232,7 @@
         <v>45419</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61305,7 +61305,7 @@
         <v>44552</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61378,7 +61378,7 @@
         <v>44579</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>44579</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>44579</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>44540</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61690,7 +61690,7 @@
         <v>44911</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         <v>44911</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61846,7 +61846,7 @@
         <v>44540</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>44911</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62080,7 +62080,7 @@
         <v>45351</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>44911</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45299</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>44540</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62387,7 +62387,7 @@
         <v>45351</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>44540</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>44540</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62621,7 +62621,7 @@
         <v>44501</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62694,7 +62694,7 @@
         <v>45779</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62767,7 +62767,7 @@
         <v>46035</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62845,7 +62845,7 @@
         <v>46177</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>46203</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>

--- a/Översikt SÄFFLE.xlsx
+++ b/Översikt SÄFFLE.xlsx
@@ -601,7 +601,7 @@
         <v>45581</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45915</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45988</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44867</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>45727</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44911</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>44564</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>45203</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45902</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45237</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>45460</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>46220</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>44673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45665</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45378</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>44787</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44505</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45012</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>45912</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>45384</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45988</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45534</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45106</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>46280</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>45644</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>45397</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>45323</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>45832</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>45646</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>45728</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46304</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44943</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>45432</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45841</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45763</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>45203</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>44589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45162</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44936</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44046</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>44943</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>45841</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44512</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44629</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44735</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44830</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44508</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>44580</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>44552</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44886</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44750</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>44552</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>44581</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44776</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44824</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>44748</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44735</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>44745</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44494</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44512</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>44602</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>44624</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44543</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>44505</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>44676</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>44629</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>44719</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44780</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
         <v>44780</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44511</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44846</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44840</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44840</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>44557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44711</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44861</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44780</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44607</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>44607</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>44602</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44868</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44629</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>44616</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44649</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44546</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44550</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44538</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44819</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44806</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44526</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44616</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44719</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44644</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44826</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44683</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44686</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>45877</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44518</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44627</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45817</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>45888</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45387</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44829</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45834</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>45720</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45712</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45403</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45208</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45890</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44671</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45893</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45893</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45893</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45893</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45251</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45895</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44501</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45418</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>44909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45898</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44671</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45516</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45516</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>44777</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45902</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45425</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45888</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45901</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45012</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45904</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45904</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45901</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45910</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45912</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45912</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45931</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>46164</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>45597</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45805</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>45915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>46164</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45425</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>45572</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45924</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44608</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45040</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45924</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44952</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>46167</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45925</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45237</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45555</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45631</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45106</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45433</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45367</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>46170</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>46170</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45931</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45471</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46170</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>46170</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>46170</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>46170</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>46175</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45372</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45245</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45394</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45253</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>44825</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45937</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45107</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>46174</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44998</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45943</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45392</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45385</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45428</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44823</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45944</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>46176</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>46177</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45471</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45457</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45945</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45386</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44929</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45261</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45558</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45454</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45946</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44868</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45237</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45070</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44550</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45949</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45950</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45457</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45523</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45358</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45062</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>44523</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46182</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45522</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45880</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45495</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45149</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45127</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>44911</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45667</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44916</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45266</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45961</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44546</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>46062</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44861</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45147</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45411</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45365</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45324</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45055</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45356</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45719</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44509</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44709</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45005</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>46191</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45977</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45278</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45279</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45975</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45975</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45474</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>44921</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45361</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45573</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45477</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>44959</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44945</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45156</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45980</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>46203</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>46183</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>44938</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45635</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45982</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45982</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45133</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46206</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45278</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45176</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>44881</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>44886</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45173</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45439</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45983</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>46209</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45988</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>46209</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>46209</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45988</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45677</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>46105</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>46209</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45337</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45988</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>46209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45988</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45988</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>46209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45107</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45667</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>45992</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45989</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45712</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>44734</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45453</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45989</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45989</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45107</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45993</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>45993</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45747</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45441</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>45707</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45603</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>45995</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45685</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45995</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45576</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45639</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45639</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45380</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45988</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45988</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>46006</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45988</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45988</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45646</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45784</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>45369</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>46233</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>46232</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>45783</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>46232</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>46232</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>46279</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26171,7 +26171,7 @@
         <v>46279</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>46010</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46237</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45736</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>46237</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>46237</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45681</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>46279</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>46237</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>46237</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>45427</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45555</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>45790</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>45790</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>46281</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>45790</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45720</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>44881</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45790</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45790</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45790</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45306</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>46030</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46281</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46030</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>46030</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>46034</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>46283</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45791</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45454</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45791</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45791</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45707</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>45796</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
         <v>46283</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>46283</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>46037</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45323</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>46287</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>46041</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>46287</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>46041</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>45910</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45895</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>46043</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45638</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>45989</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29740,7 +29740,7 @@
         <v>45239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>46046</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>46045</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>46046</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>44819</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>46045</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>46045</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45341</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45799</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45800</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>46055</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>46055</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>45520</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30689,7 +30689,7 @@
         <v>44881</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>46058</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>46289</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>45358</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>45582</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44872</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45503</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45615</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45630</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45807</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>46290</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45607</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45811</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45811</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>46059</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45575</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45771</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45811</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45419</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46290</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32154,7 +32154,7 @@
         <v>46290</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>45813</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>46065</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32373,7 +32373,7 @@
         <v>45757</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32446,7 +32446,7 @@
         <v>45818</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45623</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45646</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45763</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45761</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>45646</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32884,7 +32884,7 @@
         <v>45817</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>46072</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>46251</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45342</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>46251</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>46251</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>46073</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>46253</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>46079</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>46078</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45825</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>46083</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>46083</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>46251</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>46083</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>46083</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>46083</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45831</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45831</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>45831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>46295</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>46050</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45832</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>46255</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>46087</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>46087</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>46087</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>46086</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>45989</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>46090</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35084,7 +35084,7 @@
         <v>46090</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45835</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>46090</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>46093</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>46092</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35454,7 +35454,7 @@
         <v>46093</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>46297</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35600,7 +35600,7 @@
         <v>46297</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>46300</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>46094</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45841</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35892,7 +35892,7 @@
         <v>45842</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>46255</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>46101</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>46101</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45832</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45358</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>46105</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>46104</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>45847</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>45847</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45847</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44509</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>45589</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45847</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
         <v>45808</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>44512</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>46106</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>46258</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>46111</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46111</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>46108</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>46304</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>45516</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37581,7 +37581,7 @@
         <v>46119</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45253</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37727,7 +37727,7 @@
         <v>46119</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45874</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45420</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45874</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>46122</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>45428</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>45871</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>45729</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45537</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45746</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>44564</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45310</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45769</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>44993</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45631</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45497</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>45050</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45050</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45524</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>46134</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>44606</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>46134</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39338,7 +39338,7 @@
         <v>45883</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39416,7 +39416,7 @@
         <v>45148</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45113</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39562,7 +39562,7 @@
         <v>45113</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45075</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>44876</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45194</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>45534</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45491</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>45547</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>45931</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>46262</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>44762</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45831</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>46310</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45874</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>46266</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45771</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>46309</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>46309</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>45481</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45894</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45343</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46266</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>44572</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>44879</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44523</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>46266</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44627</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>45728</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41533,7 +41533,7 @@
         <v>45704</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>45575</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45617</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45807</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45807</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45387</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>46309</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>45932</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>44910</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>46309</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>46311</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45820</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>46314</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42502,7 +42502,7 @@
         <v>45706</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45905</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45779</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45966</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>44580</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>45740</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>44720</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45231</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>46269</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45233</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>46113</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45098</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>46309</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>46269</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>45012</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45922</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>45880</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45735</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45874</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45912</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>46314</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>46314</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>46139</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>45569</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>45855</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>46273</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46139</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45874</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44551,7 +44551,7 @@
         <v>45685</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>45932</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>46308</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>44574</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45896</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45740</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>45727</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>46273</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>46139</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>44943</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>46079</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45564</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45847</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45222</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45609</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45729,7 +45729,7 @@
         <v>45714</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45802,7 +45802,7 @@
         <v>44985</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45875,7 +45875,7 @@
         <v>44659</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>44678</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>46317</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>45735</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>46317</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>46315</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45595</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>46142</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45707</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>46317</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45280</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         <v>46146</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>44980</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>46148</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46897,7 +46897,7 @@
         <v>44745</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>45238</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>45426</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>46149</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47189,7 +47189,7 @@
         <v>45559</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>44679</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>45156</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45397</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45168</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>45095</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47627,7 +47627,7 @@
         <v>45379</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>44994</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45603</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>46154</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45068</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>46155</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>45266</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45837</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45716</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46198</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>46059</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45890</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45542</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45825</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48649,7 +48649,7 @@
         <v>45237</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48722,7 +48722,7 @@
         <v>45006</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45567</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48868,7 +48868,7 @@
         <v>45471</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48941,7 +48941,7 @@
         <v>45189</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>44509</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>44993</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49160,7 +49160,7 @@
         <v>44973</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         <v>45267</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45672</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49379,7 +49379,7 @@
         <v>45699</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>45189</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45005</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45113</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45113</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45692</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45692</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>44564</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49968,7 +49968,7 @@
         <v>45012</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>45021</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45677</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45775</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>44830</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45171</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>44880</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45711</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45676</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>44538</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45586</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45253</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45525</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>45720</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>44629</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45191</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45082</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>45611</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45249</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>45721</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>44812</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45226</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51574,7 +51574,7 @@
         <v>44813</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>44936</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45229</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51793,7 +51793,7 @@
         <v>44881</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45771</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>44880</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>45609</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>45078</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45747</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45089</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>45740</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45278</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45548</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45356</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52616,7 +52616,7 @@
         <v>45099</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52689,7 +52689,7 @@
         <v>44758</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
         <v>45368</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45063</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>44509</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45356</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45331</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53132,7 +53132,7 @@
         <v>45273</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45398</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45191</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>44976</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>45374</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45374</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45425</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45266</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>44994</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>45603</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45204</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45558</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>45348</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>45355</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>45607</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45314</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>44509</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45527</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45282</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>45582</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45044</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>45723</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45393</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45719</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45191</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45460</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45146</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45534</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45334</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45667</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>45089</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>44603</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>44550</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45439</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45625</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45506</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>44581</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>44607</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45146</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45711</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>44587</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>44606</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56213,7 +56213,7 @@
         <v>45621</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56286,7 +56286,7 @@
         <v>45313</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56359,7 +56359,7 @@
         <v>45107</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>44635</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56505,7 +56505,7 @@
         <v>45098</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56578,7 +56578,7 @@
         <v>44663</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>45704</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56724,7 +56724,7 @@
         <v>45147</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56797,7 +56797,7 @@
         <v>45583</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45222</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -56943,7 +56943,7 @@
         <v>44763</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         <v>45237</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45769</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45171</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57245,7 +57245,7 @@
         <v>45211</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57318,7 +57318,7 @@
         <v>45659</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57391,7 +57391,7 @@
         <v>45212</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>44823</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57537,7 +57537,7 @@
         <v>45681</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
         <v>45191</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45699</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57761,7 +57761,7 @@
         <v>45729</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57839,7 +57839,7 @@
         <v>45223</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57912,7 +57912,7 @@
         <v>45517</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45278</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45278</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>45295</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58214,7 +58214,7 @@
         <v>45278</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>45180</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>45733</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45728</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45278</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>44853</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45352</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45330</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>44988</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45258</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -58949,7 +58949,7 @@
         <v>44938</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>45264</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59095,7 +59095,7 @@
         <v>44852</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45098</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59241,7 +59241,7 @@
         <v>45239</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>44868</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59387,7 +59387,7 @@
         <v>45281</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45736</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45728</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>44623</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45700</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>45527</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45301</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>44924</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>45728</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60044,7 +60044,7 @@
         <v>45211</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60117,7 +60117,7 @@
         <v>45740</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>45740</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60273,7 +60273,7 @@
         <v>45621</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>45597</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>44900</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>44960</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45608</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45391</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60711,7 +60711,7 @@
         <v>45450</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60789,7 +60789,7 @@
         <v>45040</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60862,7 +60862,7 @@
         <v>44824</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60935,7 +60935,7 @@
         <v>45572</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61008,7 +61008,7 @@
         <v>44745</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>45271</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61154,7 +61154,7 @@
         <v>44763</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61232,7 +61232,7 @@
         <v>45419</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61305,7 +61305,7 @@
         <v>44552</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61378,7 +61378,7 @@
         <v>44579</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61456,7 +61456,7 @@
         <v>44579</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61534,7 +61534,7 @@
         <v>44579</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>44540</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61690,7 +61690,7 @@
         <v>44911</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61768,7 +61768,7 @@
         <v>44911</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61846,7 +61846,7 @@
         <v>44540</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>44911</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62002,7 +62002,7 @@
         <v>44540</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62080,7 +62080,7 @@
         <v>45351</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>44911</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45299</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>44540</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62387,7 +62387,7 @@
         <v>45351</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>44540</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>44540</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62621,7 +62621,7 @@
         <v>44501</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62694,7 +62694,7 @@
         <v>45779</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62767,7 +62767,7 @@
         <v>46035</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62845,7 +62845,7 @@
         <v>46177</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>46203</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
